--- a/plantillas/82.xlsx
+++ b/plantillas/82.xlsx
@@ -59,7 +59,7 @@
     <definedName name="MARCA_45">Listas!$AV$2:$AV$2</definedName>
     <definedName name="MARCA_46">Listas!$AW$2:$AW$3</definedName>
     <definedName name="MARCA_47">Listas!$AX$2:$AX$6</definedName>
-    <definedName name="MARCA_48">Listas!$AY$2:$AY$10</definedName>
+    <definedName name="MARCA_48">Listas!$AY$2:$AY$9</definedName>
     <definedName name="MARCA_49">Listas!$AZ$2:$AZ$3</definedName>
     <definedName name="MARCA_50">Listas!$BA$2:$BA$23</definedName>
     <definedName name="MARCA_51">Listas!$BB$2:$BB$19</definedName>
@@ -673,11 +673,11 @@
       <c r="A3" s="5" t="n"/>
       <c r="B3" s="5" t="n"/>
       <c r="C3" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B3,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B3,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D3" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B3,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B3,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E3" s="8" t="n"/>
@@ -697,11 +697,11 @@
       <c r="A4" s="5" t="n"/>
       <c r="B4" s="5" t="n"/>
       <c r="C4" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B4,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B4,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D4" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B4,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B4,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E4" s="8" t="n"/>
@@ -721,11 +721,11 @@
       <c r="A5" s="5" t="n"/>
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B5,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B5,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D5" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B5,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B5,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E5" s="8" t="n"/>
@@ -745,11 +745,11 @@
       <c r="A6" s="5" t="n"/>
       <c r="B6" s="5" t="n"/>
       <c r="C6" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B6,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B6,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D6" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B6,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B6,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E6" s="8" t="n"/>
@@ -764,11 +764,11 @@
       <c r="A7" s="5" t="n"/>
       <c r="B7" s="5" t="n"/>
       <c r="C7" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B7,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B7,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D7" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B7,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B7,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E7" s="8" t="n"/>
@@ -783,11 +783,11 @@
       <c r="A8" s="5" t="n"/>
       <c r="B8" s="5" t="n"/>
       <c r="C8" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B8,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B8,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D8" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B8,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B8,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E8" s="8" t="n"/>
@@ -802,11 +802,11 @@
       <c r="A9" s="5" t="n"/>
       <c r="B9" s="5" t="n"/>
       <c r="C9" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B9,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B9,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D9" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B9,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B9,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E9" s="8" t="n"/>
@@ -821,11 +821,11 @@
       <c r="A10" s="5" t="n"/>
       <c r="B10" s="5" t="n"/>
       <c r="C10" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B10,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B10,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D10" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B10,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B10,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E10" s="8" t="n"/>
@@ -840,11 +840,11 @@
       <c r="A11" s="5" t="n"/>
       <c r="B11" s="5" t="n"/>
       <c r="C11" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B11,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B11,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D11" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B11,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B11,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E11" s="8" t="n"/>
@@ -859,11 +859,11 @@
       <c r="A12" s="5" t="n"/>
       <c r="B12" s="5" t="n"/>
       <c r="C12" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B12,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B12,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D12" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B12,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B12,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E12" s="8" t="n"/>
@@ -878,11 +878,11 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="n"/>
       <c r="C13" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B13,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B13,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D13" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B13,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B13,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E13" s="8" t="n"/>
@@ -897,11 +897,11 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="n"/>
       <c r="C14" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B14,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B14,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D14" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B14,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B14,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E14" s="8" t="n"/>
@@ -916,11 +916,11 @@
       <c r="A15" s="5" t="n"/>
       <c r="B15" s="5" t="n"/>
       <c r="C15" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B15,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B15,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D15" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B15,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B15,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E15" s="8" t="n"/>
@@ -935,11 +935,11 @@
       <c r="A16" s="5" t="n"/>
       <c r="B16" s="5" t="n"/>
       <c r="C16" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B16,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B16,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D16" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B16,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B16,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E16" s="8" t="n"/>
@@ -954,11 +954,11 @@
       <c r="A17" s="5" t="n"/>
       <c r="B17" s="5" t="n"/>
       <c r="C17" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B17,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B17,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D17" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B17,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B17,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E17" s="8" t="n"/>
@@ -973,11 +973,11 @@
       <c r="A18" s="5" t="n"/>
       <c r="B18" s="5" t="n"/>
       <c r="C18" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B18,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B18,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D18" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B18,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B18,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E18" s="8" t="n"/>
@@ -992,11 +992,11 @@
       <c r="A19" s="5" t="n"/>
       <c r="B19" s="5" t="n"/>
       <c r="C19" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B19,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B19,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D19" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B19,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B19,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E19" s="8" t="n"/>
@@ -1011,11 +1011,11 @@
       <c r="A20" s="5" t="n"/>
       <c r="B20" s="5" t="n"/>
       <c r="C20" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B20,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B20,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D20" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B20,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B20,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E20" s="8" t="n"/>
@@ -1030,11 +1030,11 @@
       <c r="A21" s="5" t="n"/>
       <c r="B21" s="5" t="n"/>
       <c r="C21" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B21,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B21,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D21" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B21,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B21,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E21" s="8" t="n"/>
@@ -1049,11 +1049,11 @@
       <c r="A22" s="5" t="n"/>
       <c r="B22" s="5" t="n"/>
       <c r="C22" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B22,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B22,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D22" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B22,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B22,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E22" s="8" t="n"/>
@@ -1068,11 +1068,11 @@
       <c r="A23" s="5" t="n"/>
       <c r="B23" s="5" t="n"/>
       <c r="C23" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B23,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B23,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D23" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B23,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B23,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E23" s="8" t="n"/>
@@ -1087,11 +1087,11 @@
       <c r="A24" s="5" t="n"/>
       <c r="B24" s="5" t="n"/>
       <c r="C24" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B24,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B24,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D24" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B24,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B24,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E24" s="8" t="n"/>
@@ -1106,11 +1106,11 @@
       <c r="A25" s="5" t="n"/>
       <c r="B25" s="5" t="n"/>
       <c r="C25" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B25,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B25,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D25" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B25,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B25,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E25" s="8" t="n"/>
@@ -1125,11 +1125,11 @@
       <c r="A26" s="5" t="n"/>
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B26,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B26,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D26" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B26,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B26,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E26" s="8" t="n"/>
@@ -1144,11 +1144,11 @@
       <c r="A27" s="5" t="n"/>
       <c r="B27" s="5" t="n"/>
       <c r="C27" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B27,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B27,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D27" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B27,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B27,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E27" s="8" t="n"/>
@@ -1163,11 +1163,11 @@
       <c r="A28" s="5" t="n"/>
       <c r="B28" s="5" t="n"/>
       <c r="C28" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B28,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B28,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D28" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B28,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B28,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E28" s="8" t="n"/>
@@ -1182,11 +1182,11 @@
       <c r="A29" s="5" t="n"/>
       <c r="B29" s="5" t="n"/>
       <c r="C29" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B29,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B29,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D29" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B29,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B29,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E29" s="8" t="n"/>
@@ -1201,11 +1201,11 @@
       <c r="A30" s="5" t="n"/>
       <c r="B30" s="5" t="n"/>
       <c r="C30" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B30,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B30,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D30" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B30,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B30,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E30" s="8" t="n"/>
@@ -1220,11 +1220,11 @@
       <c r="A31" s="5" t="n"/>
       <c r="B31" s="5" t="n"/>
       <c r="C31" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B31,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B31,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D31" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B31,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B31,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E31" s="8" t="n"/>
@@ -1239,11 +1239,11 @@
       <c r="A32" s="5" t="n"/>
       <c r="B32" s="5" t="n"/>
       <c r="C32" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B32,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B32,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D32" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B32,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B32,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E32" s="8" t="n"/>
@@ -1258,11 +1258,11 @@
       <c r="A33" s="5" t="n"/>
       <c r="B33" s="5" t="n"/>
       <c r="C33" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B33,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B33,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D33" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B33,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B33,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E33" s="8" t="n"/>
@@ -1277,11 +1277,11 @@
       <c r="A34" s="5" t="n"/>
       <c r="B34" s="5" t="n"/>
       <c r="C34" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B34,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B34,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D34" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B34,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B34,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E34" s="8" t="n"/>
@@ -1296,11 +1296,11 @@
       <c r="A35" s="5" t="n"/>
       <c r="B35" s="5" t="n"/>
       <c r="C35" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B35,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B35,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D35" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B35,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B35,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E35" s="8" t="n"/>
@@ -1315,11 +1315,11 @@
       <c r="A36" s="5" t="n"/>
       <c r="B36" s="5" t="n"/>
       <c r="C36" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B36,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B36,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D36" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B36,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B36,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E36" s="8" t="n"/>
@@ -1334,11 +1334,11 @@
       <c r="A37" s="5" t="n"/>
       <c r="B37" s="5" t="n"/>
       <c r="C37" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B37,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B37,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D37" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B37,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B37,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E37" s="8" t="n"/>
@@ -1353,11 +1353,11 @@
       <c r="A38" s="5" t="n"/>
       <c r="B38" s="5" t="n"/>
       <c r="C38" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B38,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B38,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D38" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B38,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B38,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E38" s="8" t="n"/>
@@ -1372,11 +1372,11 @@
       <c r="A39" s="5" t="n"/>
       <c r="B39" s="5" t="n"/>
       <c r="C39" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B39,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B39,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D39" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B39,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B39,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E39" s="8" t="n"/>
@@ -1391,11 +1391,11 @@
       <c r="A40" s="5" t="n"/>
       <c r="B40" s="5" t="n"/>
       <c r="C40" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B40,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B40,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D40" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B40,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B40,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E40" s="8" t="n"/>
@@ -1410,11 +1410,11 @@
       <c r="A41" s="5" t="n"/>
       <c r="B41" s="5" t="n"/>
       <c r="C41" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B41,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B41,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D41" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B41,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B41,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E41" s="8" t="n"/>
@@ -1429,11 +1429,11 @@
       <c r="A42" s="5" t="n"/>
       <c r="B42" s="5" t="n"/>
       <c r="C42" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B42,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B42,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D42" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B42,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B42,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E42" s="8" t="n"/>
@@ -1448,11 +1448,11 @@
       <c r="A43" s="5" t="n"/>
       <c r="B43" s="5" t="n"/>
       <c r="C43" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B43,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B43,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D43" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B43,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B43,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E43" s="8" t="n"/>
@@ -1467,11 +1467,11 @@
       <c r="A44" s="5" t="n"/>
       <c r="B44" s="5" t="n"/>
       <c r="C44" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B44,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B44,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D44" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B44,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B44,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E44" s="8" t="n"/>
@@ -1486,11 +1486,11 @@
       <c r="A45" s="5" t="n"/>
       <c r="B45" s="5" t="n"/>
       <c r="C45" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B45,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B45,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D45" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B45,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B45,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E45" s="8" t="n"/>
@@ -1505,11 +1505,11 @@
       <c r="A46" s="5" t="n"/>
       <c r="B46" s="5" t="n"/>
       <c r="C46" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B46,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B46,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D46" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B46,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B46,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E46" s="8" t="n"/>
@@ -1524,11 +1524,11 @@
       <c r="A47" s="5" t="n"/>
       <c r="B47" s="5" t="n"/>
       <c r="C47" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B47,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B47,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D47" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B47,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B47,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E47" s="8" t="n"/>
@@ -1543,11 +1543,11 @@
       <c r="A48" s="5" t="n"/>
       <c r="B48" s="5" t="n"/>
       <c r="C48" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B48,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B48,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D48" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B48,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B48,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E48" s="8" t="n"/>
@@ -1562,11 +1562,11 @@
       <c r="A49" s="5" t="n"/>
       <c r="B49" s="5" t="n"/>
       <c r="C49" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B49,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B49,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D49" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B49,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B49,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E49" s="8" t="n"/>
@@ -1581,11 +1581,11 @@
       <c r="A50" s="5" t="n"/>
       <c r="B50" s="5" t="n"/>
       <c r="C50" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B50,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B50,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D50" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B50,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B50,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E50" s="8" t="n"/>
@@ -1600,11 +1600,11 @@
       <c r="A51" s="5" t="n"/>
       <c r="B51" s="5" t="n"/>
       <c r="C51" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B51,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B51,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D51" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B51,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B51,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E51" s="8" t="n"/>
@@ -1619,11 +1619,11 @@
       <c r="A52" s="5" t="n"/>
       <c r="B52" s="5" t="n"/>
       <c r="C52" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B52,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B52,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D52" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B52,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B52,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E52" s="8" t="n"/>
@@ -1638,11 +1638,11 @@
       <c r="A53" s="5" t="n"/>
       <c r="B53" s="5" t="n"/>
       <c r="C53" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B53,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B53,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D53" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B53,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B53,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E53" s="8" t="n"/>
@@ -1657,11 +1657,11 @@
       <c r="A54" s="5" t="n"/>
       <c r="B54" s="5" t="n"/>
       <c r="C54" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B54,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B54,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D54" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B54,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B54,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E54" s="8" t="n"/>
@@ -1676,11 +1676,11 @@
       <c r="A55" s="5" t="n"/>
       <c r="B55" s="5" t="n"/>
       <c r="C55" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B55,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B55,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D55" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B55,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B55,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E55" s="8" t="n"/>
@@ -1695,11 +1695,11 @@
       <c r="A56" s="5" t="n"/>
       <c r="B56" s="5" t="n"/>
       <c r="C56" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B56,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B56,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D56" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B56,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B56,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E56" s="8" t="n"/>
@@ -1714,11 +1714,11 @@
       <c r="A57" s="5" t="n"/>
       <c r="B57" s="5" t="n"/>
       <c r="C57" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B57,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B57,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D57" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B57,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B57,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E57" s="8" t="n"/>
@@ -1733,11 +1733,11 @@
       <c r="A58" s="5" t="n"/>
       <c r="B58" s="5" t="n"/>
       <c r="C58" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B58,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B58,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D58" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B58,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B58,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E58" s="8" t="n"/>
@@ -1752,11 +1752,11 @@
       <c r="A59" s="5" t="n"/>
       <c r="B59" s="5" t="n"/>
       <c r="C59" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B59,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B59,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D59" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B59,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B59,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E59" s="8" t="n"/>
@@ -1771,11 +1771,11 @@
       <c r="A60" s="5" t="n"/>
       <c r="B60" s="5" t="n"/>
       <c r="C60" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B60,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B60,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D60" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B60,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B60,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E60" s="8" t="n"/>
@@ -1790,11 +1790,11 @@
       <c r="A61" s="5" t="n"/>
       <c r="B61" s="5" t="n"/>
       <c r="C61" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B61,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B61,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D61" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B61,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B61,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E61" s="8" t="n"/>
@@ -1809,11 +1809,11 @@
       <c r="A62" s="5" t="n"/>
       <c r="B62" s="5" t="n"/>
       <c r="C62" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B62,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B62,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D62" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B62,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B62,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E62" s="8" t="n"/>
@@ -1828,11 +1828,11 @@
       <c r="A63" s="5" t="n"/>
       <c r="B63" s="5" t="n"/>
       <c r="C63" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B63,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B63,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D63" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B63,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B63,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E63" s="8" t="n"/>
@@ -1847,11 +1847,11 @@
       <c r="A64" s="5" t="n"/>
       <c r="B64" s="5" t="n"/>
       <c r="C64" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B64,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B64,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D64" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B64,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B64,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E64" s="8" t="n"/>
@@ -1866,11 +1866,11 @@
       <c r="A65" s="5" t="n"/>
       <c r="B65" s="5" t="n"/>
       <c r="C65" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B65,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B65,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D65" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B65,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B65,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E65" s="8" t="n"/>
@@ -1885,11 +1885,11 @@
       <c r="A66" s="5" t="n"/>
       <c r="B66" s="5" t="n"/>
       <c r="C66" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B66,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B66,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D66" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B66,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B66,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E66" s="8" t="n"/>
@@ -1904,11 +1904,11 @@
       <c r="A67" s="5" t="n"/>
       <c r="B67" s="5" t="n"/>
       <c r="C67" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B67,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B67,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D67" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B67,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B67,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E67" s="8" t="n"/>
@@ -1923,11 +1923,11 @@
       <c r="A68" s="5" t="n"/>
       <c r="B68" s="5" t="n"/>
       <c r="C68" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B68,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B68,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D68" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B68,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B68,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E68" s="8" t="n"/>
@@ -1942,11 +1942,11 @@
       <c r="A69" s="5" t="n"/>
       <c r="B69" s="5" t="n"/>
       <c r="C69" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B69,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B69,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D69" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B69,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B69,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E69" s="8" t="n"/>
@@ -1961,11 +1961,11 @@
       <c r="A70" s="5" t="n"/>
       <c r="B70" s="5" t="n"/>
       <c r="C70" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B70,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B70,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D70" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B70,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B70,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E70" s="8" t="n"/>
@@ -1980,11 +1980,11 @@
       <c r="A71" s="5" t="n"/>
       <c r="B71" s="5" t="n"/>
       <c r="C71" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B71,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B71,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D71" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B71,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B71,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E71" s="8" t="n"/>
@@ -1999,11 +1999,11 @@
       <c r="A72" s="5" t="n"/>
       <c r="B72" s="5" t="n"/>
       <c r="C72" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B72,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B72,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D72" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B72,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B72,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E72" s="8" t="n"/>
@@ -2018,11 +2018,11 @@
       <c r="A73" s="5" t="n"/>
       <c r="B73" s="5" t="n"/>
       <c r="C73" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B73,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B73,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D73" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B73,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B73,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E73" s="8" t="n"/>
@@ -2037,11 +2037,11 @@
       <c r="A74" s="5" t="n"/>
       <c r="B74" s="5" t="n"/>
       <c r="C74" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B74,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B74,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D74" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B74,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B74,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E74" s="8" t="n"/>
@@ -2056,11 +2056,11 @@
       <c r="A75" s="5" t="n"/>
       <c r="B75" s="5" t="n"/>
       <c r="C75" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B75,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B75,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D75" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B75,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B75,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E75" s="8" t="n"/>
@@ -2075,11 +2075,11 @@
       <c r="A76" s="5" t="n"/>
       <c r="B76" s="5" t="n"/>
       <c r="C76" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B76,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B76,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D76" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B76,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B76,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E76" s="8" t="n"/>
@@ -2094,11 +2094,11 @@
       <c r="A77" s="5" t="n"/>
       <c r="B77" s="5" t="n"/>
       <c r="C77" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B77,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B77,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D77" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B77,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B77,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E77" s="8" t="n"/>
@@ -2113,11 +2113,11 @@
       <c r="A78" s="5" t="n"/>
       <c r="B78" s="5" t="n"/>
       <c r="C78" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B78,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B78,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D78" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B78,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B78,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E78" s="8" t="n"/>
@@ -2132,11 +2132,11 @@
       <c r="A79" s="5" t="n"/>
       <c r="B79" s="5" t="n"/>
       <c r="C79" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B79,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B79,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D79" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B79,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B79,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E79" s="8" t="n"/>
@@ -2151,11 +2151,11 @@
       <c r="A80" s="5" t="n"/>
       <c r="B80" s="5" t="n"/>
       <c r="C80" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B80,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B80,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D80" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B80,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B80,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E80" s="8" t="n"/>
@@ -2170,11 +2170,11 @@
       <c r="A81" s="5" t="n"/>
       <c r="B81" s="5" t="n"/>
       <c r="C81" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B81,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B81,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D81" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B81,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B81,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E81" s="8" t="n"/>
@@ -2189,11 +2189,11 @@
       <c r="A82" s="5" t="n"/>
       <c r="B82" s="5" t="n"/>
       <c r="C82" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B82,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B82,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D82" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B82,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B82,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E82" s="8" t="n"/>
@@ -2208,11 +2208,11 @@
       <c r="A83" s="5" t="n"/>
       <c r="B83" s="5" t="n"/>
       <c r="C83" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B83,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B83,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D83" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B83,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B83,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E83" s="8" t="n"/>
@@ -2227,11 +2227,11 @@
       <c r="A84" s="5" t="n"/>
       <c r="B84" s="5" t="n"/>
       <c r="C84" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B84,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B84,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D84" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B84,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B84,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E84" s="8" t="n"/>
@@ -2246,11 +2246,11 @@
       <c r="A85" s="5" t="n"/>
       <c r="B85" s="5" t="n"/>
       <c r="C85" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B85,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B85,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D85" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B85,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B85,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E85" s="8" t="n"/>
@@ -2265,11 +2265,11 @@
       <c r="A86" s="5" t="n"/>
       <c r="B86" s="5" t="n"/>
       <c r="C86" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B86,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B86,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D86" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B86,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B86,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E86" s="8" t="n"/>
@@ -2284,11 +2284,11 @@
       <c r="A87" s="5" t="n"/>
       <c r="B87" s="5" t="n"/>
       <c r="C87" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B87,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B87,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D87" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B87,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B87,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E87" s="8" t="n"/>
@@ -2303,11 +2303,11 @@
       <c r="A88" s="5" t="n"/>
       <c r="B88" s="5" t="n"/>
       <c r="C88" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B88,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B88,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D88" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B88,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B88,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E88" s="8" t="n"/>
@@ -2322,11 +2322,11 @@
       <c r="A89" s="5" t="n"/>
       <c r="B89" s="5" t="n"/>
       <c r="C89" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B89,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B89,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D89" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B89,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B89,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E89" s="8" t="n"/>
@@ -2341,11 +2341,11 @@
       <c r="A90" s="5" t="n"/>
       <c r="B90" s="5" t="n"/>
       <c r="C90" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B90,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B90,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D90" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B90,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B90,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E90" s="8" t="n"/>
@@ -2360,11 +2360,11 @@
       <c r="A91" s="5" t="n"/>
       <c r="B91" s="5" t="n"/>
       <c r="C91" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B91,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B91,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D91" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B91,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B91,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E91" s="8" t="n"/>
@@ -2379,11 +2379,11 @@
       <c r="A92" s="5" t="n"/>
       <c r="B92" s="5" t="n"/>
       <c r="C92" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B92,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B92,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D92" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B92,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B92,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E92" s="8" t="n"/>
@@ -2398,11 +2398,11 @@
       <c r="A93" s="5" t="n"/>
       <c r="B93" s="5" t="n"/>
       <c r="C93" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B93,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B93,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D93" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B93,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B93,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E93" s="8" t="n"/>
@@ -2417,11 +2417,11 @@
       <c r="A94" s="5" t="n"/>
       <c r="B94" s="5" t="n"/>
       <c r="C94" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B94,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B94,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D94" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B94,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B94,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E94" s="8" t="n"/>
@@ -2436,11 +2436,11 @@
       <c r="A95" s="5" t="n"/>
       <c r="B95" s="5" t="n"/>
       <c r="C95" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B95,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B95,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D95" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B95,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B95,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E95" s="8" t="n"/>
@@ -2455,11 +2455,11 @@
       <c r="A96" s="5" t="n"/>
       <c r="B96" s="5" t="n"/>
       <c r="C96" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B96,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B96,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D96" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B96,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B96,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E96" s="8" t="n"/>
@@ -2474,11 +2474,11 @@
       <c r="A97" s="5" t="n"/>
       <c r="B97" s="5" t="n"/>
       <c r="C97" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B97,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B97,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D97" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B97,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B97,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E97" s="8" t="n"/>
@@ -2493,11 +2493,11 @@
       <c r="A98" s="5" t="n"/>
       <c r="B98" s="5" t="n"/>
       <c r="C98" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B98,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B98,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D98" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B98,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B98,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E98" s="8" t="n"/>
@@ -2512,11 +2512,11 @@
       <c r="A99" s="5" t="n"/>
       <c r="B99" s="5" t="n"/>
       <c r="C99" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B99,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B99,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D99" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B99,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B99,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E99" s="8" t="n"/>
@@ -2531,11 +2531,11 @@
       <c r="A100" s="5" t="n"/>
       <c r="B100" s="5" t="n"/>
       <c r="C100" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B100,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B100,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D100" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B100,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B100,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E100" s="8" t="n"/>
@@ -2550,11 +2550,11 @@
       <c r="A101" s="5" t="n"/>
       <c r="B101" s="5" t="n"/>
       <c r="C101" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B101,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B101,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D101" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B101,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B101,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E101" s="8" t="n"/>
@@ -2569,11 +2569,11 @@
       <c r="A102" s="5" t="n"/>
       <c r="B102" s="5" t="n"/>
       <c r="C102" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B102,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B102,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D102" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B102,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B102,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E102" s="8" t="n"/>
@@ -2588,11 +2588,11 @@
       <c r="A103" s="5" t="n"/>
       <c r="B103" s="5" t="n"/>
       <c r="C103" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B103,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B103,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D103" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B103,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B103,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E103" s="8" t="n"/>
@@ -2607,11 +2607,11 @@
       <c r="A104" s="5" t="n"/>
       <c r="B104" s="5" t="n"/>
       <c r="C104" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B104,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B104,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D104" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B104,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B104,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E104" s="8" t="n"/>
@@ -2626,11 +2626,11 @@
       <c r="A105" s="5" t="n"/>
       <c r="B105" s="5" t="n"/>
       <c r="C105" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B105,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B105,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D105" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B105,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B105,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E105" s="8" t="n"/>
@@ -2645,11 +2645,11 @@
       <c r="A106" s="5" t="n"/>
       <c r="B106" s="5" t="n"/>
       <c r="C106" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B106,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B106,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D106" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B106,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B106,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E106" s="8" t="n"/>
@@ -2664,11 +2664,11 @@
       <c r="A107" s="5" t="n"/>
       <c r="B107" s="5" t="n"/>
       <c r="C107" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B107,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B107,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D107" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B107,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B107,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E107" s="8" t="n"/>
@@ -2683,11 +2683,11 @@
       <c r="A108" s="5" t="n"/>
       <c r="B108" s="5" t="n"/>
       <c r="C108" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B108,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B108,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D108" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B108,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B108,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E108" s="8" t="n"/>
@@ -2702,11 +2702,11 @@
       <c r="A109" s="5" t="n"/>
       <c r="B109" s="5" t="n"/>
       <c r="C109" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B109,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B109,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D109" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B109,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B109,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E109" s="8" t="n"/>
@@ -2721,11 +2721,11 @@
       <c r="A110" s="5" t="n"/>
       <c r="B110" s="5" t="n"/>
       <c r="C110" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B110,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B110,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D110" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B110,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B110,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E110" s="8" t="n"/>
@@ -2740,11 +2740,11 @@
       <c r="A111" s="5" t="n"/>
       <c r="B111" s="5" t="n"/>
       <c r="C111" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B111,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B111,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D111" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B111,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B111,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E111" s="8" t="n"/>
@@ -2759,11 +2759,11 @@
       <c r="A112" s="5" t="n"/>
       <c r="B112" s="5" t="n"/>
       <c r="C112" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B112,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B112,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D112" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B112,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B112,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E112" s="8" t="n"/>
@@ -2778,11 +2778,11 @@
       <c r="A113" s="5" t="n"/>
       <c r="B113" s="5" t="n"/>
       <c r="C113" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B113,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B113,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D113" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B113,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B113,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E113" s="8" t="n"/>
@@ -2797,11 +2797,11 @@
       <c r="A114" s="5" t="n"/>
       <c r="B114" s="5" t="n"/>
       <c r="C114" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B114,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B114,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D114" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B114,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B114,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E114" s="8" t="n"/>
@@ -2816,11 +2816,11 @@
       <c r="A115" s="5" t="n"/>
       <c r="B115" s="5" t="n"/>
       <c r="C115" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B115,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B115,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D115" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B115,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B115,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E115" s="8" t="n"/>
@@ -2835,11 +2835,11 @@
       <c r="A116" s="5" t="n"/>
       <c r="B116" s="5" t="n"/>
       <c r="C116" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B116,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B116,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D116" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B116,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B116,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E116" s="8" t="n"/>
@@ -2854,11 +2854,11 @@
       <c r="A117" s="5" t="n"/>
       <c r="B117" s="5" t="n"/>
       <c r="C117" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B117,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B117,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D117" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B117,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B117,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E117" s="8" t="n"/>
@@ -2873,11 +2873,11 @@
       <c r="A118" s="5" t="n"/>
       <c r="B118" s="5" t="n"/>
       <c r="C118" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B118,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B118,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D118" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B118,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B118,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E118" s="8" t="n"/>
@@ -2892,11 +2892,11 @@
       <c r="A119" s="5" t="n"/>
       <c r="B119" s="5" t="n"/>
       <c r="C119" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B119,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B119,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D119" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B119,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B119,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E119" s="8" t="n"/>
@@ -2911,11 +2911,11 @@
       <c r="A120" s="5" t="n"/>
       <c r="B120" s="5" t="n"/>
       <c r="C120" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B120,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B120,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D120" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B120,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B120,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E120" s="8" t="n"/>
@@ -2930,11 +2930,11 @@
       <c r="A121" s="5" t="n"/>
       <c r="B121" s="5" t="n"/>
       <c r="C121" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B121,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B121,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D121" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B121,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B121,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E121" s="8" t="n"/>
@@ -2949,11 +2949,11 @@
       <c r="A122" s="5" t="n"/>
       <c r="B122" s="5" t="n"/>
       <c r="C122" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B122,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B122,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D122" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B122,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B122,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E122" s="8" t="n"/>
@@ -2968,11 +2968,11 @@
       <c r="A123" s="5" t="n"/>
       <c r="B123" s="5" t="n"/>
       <c r="C123" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B123,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B123,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D123" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B123,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B123,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E123" s="8" t="n"/>
@@ -2987,11 +2987,11 @@
       <c r="A124" s="5" t="n"/>
       <c r="B124" s="5" t="n"/>
       <c r="C124" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B124,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B124,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D124" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B124,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B124,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E124" s="8" t="n"/>
@@ -3006,11 +3006,11 @@
       <c r="A125" s="5" t="n"/>
       <c r="B125" s="5" t="n"/>
       <c r="C125" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B125,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B125,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D125" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B125,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B125,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E125" s="8" t="n"/>
@@ -3025,11 +3025,11 @@
       <c r="A126" s="5" t="n"/>
       <c r="B126" s="5" t="n"/>
       <c r="C126" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B126,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B126,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D126" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B126,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B126,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E126" s="8" t="n"/>
@@ -3044,11 +3044,11 @@
       <c r="A127" s="5" t="n"/>
       <c r="B127" s="5" t="n"/>
       <c r="C127" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B127,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B127,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D127" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B127,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B127,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E127" s="8" t="n"/>
@@ -3063,11 +3063,11 @@
       <c r="A128" s="5" t="n"/>
       <c r="B128" s="5" t="n"/>
       <c r="C128" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B128,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B128,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D128" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B128,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B128,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E128" s="8" t="n"/>
@@ -3082,11 +3082,11 @@
       <c r="A129" s="5" t="n"/>
       <c r="B129" s="5" t="n"/>
       <c r="C129" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B129,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B129,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D129" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B129,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B129,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E129" s="8" t="n"/>
@@ -3101,11 +3101,11 @@
       <c r="A130" s="5" t="n"/>
       <c r="B130" s="5" t="n"/>
       <c r="C130" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B130,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B130,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D130" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B130,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B130,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E130" s="8" t="n"/>
@@ -3120,11 +3120,11 @@
       <c r="A131" s="5" t="n"/>
       <c r="B131" s="5" t="n"/>
       <c r="C131" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B131,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B131,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D131" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B131,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B131,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E131" s="8" t="n"/>
@@ -3139,11 +3139,11 @@
       <c r="A132" s="5" t="n"/>
       <c r="B132" s="5" t="n"/>
       <c r="C132" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B132,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B132,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D132" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B132,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B132,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E132" s="8" t="n"/>
@@ -3158,11 +3158,11 @@
       <c r="A133" s="5" t="n"/>
       <c r="B133" s="5" t="n"/>
       <c r="C133" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B133,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B133,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D133" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B133,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B133,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E133" s="8" t="n"/>
@@ -3177,11 +3177,11 @@
       <c r="A134" s="5" t="n"/>
       <c r="B134" s="5" t="n"/>
       <c r="C134" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B134,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B134,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D134" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B134,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B134,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E134" s="8" t="n"/>
@@ -3196,11 +3196,11 @@
       <c r="A135" s="5" t="n"/>
       <c r="B135" s="5" t="n"/>
       <c r="C135" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B135,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B135,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D135" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B135,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B135,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E135" s="8" t="n"/>
@@ -3215,11 +3215,11 @@
       <c r="A136" s="5" t="n"/>
       <c r="B136" s="5" t="n"/>
       <c r="C136" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B136,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B136,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D136" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B136,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B136,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E136" s="8" t="n"/>
@@ -3234,11 +3234,11 @@
       <c r="A137" s="5" t="n"/>
       <c r="B137" s="5" t="n"/>
       <c r="C137" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B137,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B137,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D137" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B137,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B137,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E137" s="8" t="n"/>
@@ -3253,11 +3253,11 @@
       <c r="A138" s="5" t="n"/>
       <c r="B138" s="5" t="n"/>
       <c r="C138" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B138,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B138,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D138" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B138,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B138,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E138" s="8" t="n"/>
@@ -3272,11 +3272,11 @@
       <c r="A139" s="5" t="n"/>
       <c r="B139" s="5" t="n"/>
       <c r="C139" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B139,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B139,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D139" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B139,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B139,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E139" s="8" t="n"/>
@@ -3291,11 +3291,11 @@
       <c r="A140" s="5" t="n"/>
       <c r="B140" s="5" t="n"/>
       <c r="C140" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B140,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B140,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D140" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B140,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B140,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E140" s="8" t="n"/>
@@ -3310,11 +3310,11 @@
       <c r="A141" s="5" t="n"/>
       <c r="B141" s="5" t="n"/>
       <c r="C141" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B141,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B141,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D141" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B141,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B141,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E141" s="8" t="n"/>
@@ -3329,11 +3329,11 @@
       <c r="A142" s="5" t="n"/>
       <c r="B142" s="5" t="n"/>
       <c r="C142" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B142,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B142,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D142" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B142,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B142,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E142" s="8" t="n"/>
@@ -3348,11 +3348,11 @@
       <c r="A143" s="5" t="n"/>
       <c r="B143" s="5" t="n"/>
       <c r="C143" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B143,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B143,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D143" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B143,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B143,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E143" s="8" t="n"/>
@@ -3367,11 +3367,11 @@
       <c r="A144" s="5" t="n"/>
       <c r="B144" s="5" t="n"/>
       <c r="C144" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B144,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B144,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D144" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B144,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B144,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E144" s="8" t="n"/>
@@ -3386,11 +3386,11 @@
       <c r="A145" s="5" t="n"/>
       <c r="B145" s="5" t="n"/>
       <c r="C145" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B145,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B145,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D145" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B145,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B145,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E145" s="8" t="n"/>
@@ -3405,11 +3405,11 @@
       <c r="A146" s="5" t="n"/>
       <c r="B146" s="5" t="n"/>
       <c r="C146" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B146,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B146,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D146" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B146,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B146,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E146" s="8" t="n"/>
@@ -3424,11 +3424,11 @@
       <c r="A147" s="5" t="n"/>
       <c r="B147" s="5" t="n"/>
       <c r="C147" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B147,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B147,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D147" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B147,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B147,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E147" s="8" t="n"/>
@@ -3443,11 +3443,11 @@
       <c r="A148" s="5" t="n"/>
       <c r="B148" s="5" t="n"/>
       <c r="C148" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B148,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B148,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D148" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B148,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B148,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E148" s="8" t="n"/>
@@ -3462,11 +3462,11 @@
       <c r="A149" s="5" t="n"/>
       <c r="B149" s="5" t="n"/>
       <c r="C149" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B149,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B149,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D149" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B149,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B149,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E149" s="8" t="n"/>
@@ -3481,11 +3481,11 @@
       <c r="A150" s="5" t="n"/>
       <c r="B150" s="5" t="n"/>
       <c r="C150" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B150,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B150,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D150" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B150,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B150,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E150" s="8" t="n"/>
@@ -3500,11 +3500,11 @@
       <c r="A151" s="5" t="n"/>
       <c r="B151" s="5" t="n"/>
       <c r="C151" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B151,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B151,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D151" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B151,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B151,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E151" s="8" t="n"/>
@@ -3519,11 +3519,11 @@
       <c r="A152" s="5" t="n"/>
       <c r="B152" s="5" t="n"/>
       <c r="C152" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B152,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B152,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D152" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B152,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B152,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E152" s="8" t="n"/>
@@ -3538,11 +3538,11 @@
       <c r="A153" s="5" t="n"/>
       <c r="B153" s="5" t="n"/>
       <c r="C153" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B153,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B153,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D153" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B153,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B153,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E153" s="8" t="n"/>
@@ -3557,11 +3557,11 @@
       <c r="A154" s="5" t="n"/>
       <c r="B154" s="5" t="n"/>
       <c r="C154" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B154,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B154,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D154" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B154,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B154,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E154" s="8" t="n"/>
@@ -3576,11 +3576,11 @@
       <c r="A155" s="5" t="n"/>
       <c r="B155" s="5" t="n"/>
       <c r="C155" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B155,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B155,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D155" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B155,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B155,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E155" s="8" t="n"/>
@@ -3595,11 +3595,11 @@
       <c r="A156" s="5" t="n"/>
       <c r="B156" s="5" t="n"/>
       <c r="C156" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B156,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B156,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D156" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B156,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B156,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E156" s="8" t="n"/>
@@ -3614,11 +3614,11 @@
       <c r="A157" s="5" t="n"/>
       <c r="B157" s="5" t="n"/>
       <c r="C157" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B157,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B157,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D157" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B157,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B157,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E157" s="8" t="n"/>
@@ -3633,11 +3633,11 @@
       <c r="A158" s="5" t="n"/>
       <c r="B158" s="5" t="n"/>
       <c r="C158" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B158,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B158,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D158" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B158,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B158,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E158" s="8" t="n"/>
@@ -3652,11 +3652,11 @@
       <c r="A159" s="5" t="n"/>
       <c r="B159" s="5" t="n"/>
       <c r="C159" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B159,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B159,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D159" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B159,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B159,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E159" s="8" t="n"/>
@@ -3671,11 +3671,11 @@
       <c r="A160" s="5" t="n"/>
       <c r="B160" s="5" t="n"/>
       <c r="C160" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B160,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B160,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D160" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B160,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B160,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E160" s="8" t="n"/>
@@ -3690,11 +3690,11 @@
       <c r="A161" s="5" t="n"/>
       <c r="B161" s="5" t="n"/>
       <c r="C161" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B161,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B161,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D161" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B161,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B161,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E161" s="8" t="n"/>
@@ -3709,11 +3709,11 @@
       <c r="A162" s="5" t="n"/>
       <c r="B162" s="5" t="n"/>
       <c r="C162" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B162,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B162,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D162" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B162,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B162,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E162" s="8" t="n"/>
@@ -3728,11 +3728,11 @@
       <c r="A163" s="5" t="n"/>
       <c r="B163" s="5" t="n"/>
       <c r="C163" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B163,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B163,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D163" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B163,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B163,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E163" s="8" t="n"/>
@@ -3747,11 +3747,11 @@
       <c r="A164" s="5" t="n"/>
       <c r="B164" s="5" t="n"/>
       <c r="C164" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B164,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B164,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D164" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B164,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B164,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E164" s="8" t="n"/>
@@ -3766,11 +3766,11 @@
       <c r="A165" s="5" t="n"/>
       <c r="B165" s="5" t="n"/>
       <c r="C165" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B165,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B165,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D165" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B165,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B165,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E165" s="8" t="n"/>
@@ -3785,11 +3785,11 @@
       <c r="A166" s="5" t="n"/>
       <c r="B166" s="5" t="n"/>
       <c r="C166" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B166,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B166,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D166" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B166,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B166,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E166" s="8" t="n"/>
@@ -3804,11 +3804,11 @@
       <c r="A167" s="5" t="n"/>
       <c r="B167" s="5" t="n"/>
       <c r="C167" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B167,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B167,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D167" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B167,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B167,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E167" s="8" t="n"/>
@@ -3823,11 +3823,11 @@
       <c r="A168" s="5" t="n"/>
       <c r="B168" s="5" t="n"/>
       <c r="C168" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B168,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B168,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D168" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B168,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B168,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E168" s="8" t="n"/>
@@ -3842,11 +3842,11 @@
       <c r="A169" s="5" t="n"/>
       <c r="B169" s="5" t="n"/>
       <c r="C169" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B169,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B169,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D169" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B169,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B169,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E169" s="8" t="n"/>
@@ -3861,11 +3861,11 @@
       <c r="A170" s="5" t="n"/>
       <c r="B170" s="5" t="n"/>
       <c r="C170" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B170,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B170,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D170" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B170,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B170,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E170" s="8" t="n"/>
@@ -3880,11 +3880,11 @@
       <c r="A171" s="5" t="n"/>
       <c r="B171" s="5" t="n"/>
       <c r="C171" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B171,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B171,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D171" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B171,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B171,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E171" s="8" t="n"/>
@@ -3899,11 +3899,11 @@
       <c r="A172" s="5" t="n"/>
       <c r="B172" s="5" t="n"/>
       <c r="C172" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B172,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B172,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D172" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B172,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B172,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E172" s="8" t="n"/>
@@ -3918,11 +3918,11 @@
       <c r="A173" s="5" t="n"/>
       <c r="B173" s="5" t="n"/>
       <c r="C173" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B173,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B173,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D173" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B173,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B173,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E173" s="8" t="n"/>
@@ -3937,11 +3937,11 @@
       <c r="A174" s="5" t="n"/>
       <c r="B174" s="5" t="n"/>
       <c r="C174" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B174,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B174,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D174" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B174,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B174,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E174" s="8" t="n"/>
@@ -3956,11 +3956,11 @@
       <c r="A175" s="5" t="n"/>
       <c r="B175" s="5" t="n"/>
       <c r="C175" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B175,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B175,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D175" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B175,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B175,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E175" s="8" t="n"/>
@@ -3975,11 +3975,11 @@
       <c r="A176" s="5" t="n"/>
       <c r="B176" s="5" t="n"/>
       <c r="C176" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B176,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B176,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D176" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B176,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B176,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E176" s="8" t="n"/>
@@ -3994,11 +3994,11 @@
       <c r="A177" s="5" t="n"/>
       <c r="B177" s="5" t="n"/>
       <c r="C177" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B177,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B177,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D177" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B177,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B177,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E177" s="8" t="n"/>
@@ -4013,11 +4013,11 @@
       <c r="A178" s="5" t="n"/>
       <c r="B178" s="5" t="n"/>
       <c r="C178" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B178,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B178,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D178" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B178,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B178,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E178" s="8" t="n"/>
@@ -4032,11 +4032,11 @@
       <c r="A179" s="5" t="n"/>
       <c r="B179" s="5" t="n"/>
       <c r="C179" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B179,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B179,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D179" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B179,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B179,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E179" s="8" t="n"/>
@@ -4051,11 +4051,11 @@
       <c r="A180" s="5" t="n"/>
       <c r="B180" s="5" t="n"/>
       <c r="C180" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B180,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B180,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D180" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B180,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B180,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E180" s="8" t="n"/>
@@ -4070,11 +4070,11 @@
       <c r="A181" s="5" t="n"/>
       <c r="B181" s="5" t="n"/>
       <c r="C181" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B181,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B181,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D181" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B181,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B181,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E181" s="8" t="n"/>
@@ -4089,11 +4089,11 @@
       <c r="A182" s="5" t="n"/>
       <c r="B182" s="5" t="n"/>
       <c r="C182" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B182,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B182,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D182" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B182,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B182,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E182" s="8" t="n"/>
@@ -4108,11 +4108,11 @@
       <c r="A183" s="5" t="n"/>
       <c r="B183" s="5" t="n"/>
       <c r="C183" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B183,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B183,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D183" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B183,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B183,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E183" s="8" t="n"/>
@@ -4127,11 +4127,11 @@
       <c r="A184" s="5" t="n"/>
       <c r="B184" s="5" t="n"/>
       <c r="C184" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B184,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B184,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D184" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B184,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B184,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E184" s="8" t="n"/>
@@ -4146,11 +4146,11 @@
       <c r="A185" s="5" t="n"/>
       <c r="B185" s="5" t="n"/>
       <c r="C185" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B185,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B185,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D185" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B185,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B185,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E185" s="8" t="n"/>
@@ -4165,11 +4165,11 @@
       <c r="A186" s="5" t="n"/>
       <c r="B186" s="5" t="n"/>
       <c r="C186" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B186,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B186,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D186" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B186,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B186,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E186" s="8" t="n"/>
@@ -4184,11 +4184,11 @@
       <c r="A187" s="5" t="n"/>
       <c r="B187" s="5" t="n"/>
       <c r="C187" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B187,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B187,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D187" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B187,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B187,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E187" s="8" t="n"/>
@@ -4203,11 +4203,11 @@
       <c r="A188" s="5" t="n"/>
       <c r="B188" s="5" t="n"/>
       <c r="C188" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B188,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B188,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D188" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B188,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B188,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E188" s="8" t="n"/>
@@ -4222,11 +4222,11 @@
       <c r="A189" s="5" t="n"/>
       <c r="B189" s="5" t="n"/>
       <c r="C189" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B189,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B189,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D189" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B189,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B189,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E189" s="8" t="n"/>
@@ -4241,11 +4241,11 @@
       <c r="A190" s="5" t="n"/>
       <c r="B190" s="5" t="n"/>
       <c r="C190" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B190,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B190,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D190" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B190,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B190,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E190" s="8" t="n"/>
@@ -4260,11 +4260,11 @@
       <c r="A191" s="5" t="n"/>
       <c r="B191" s="5" t="n"/>
       <c r="C191" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B191,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B191,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D191" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B191,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B191,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E191" s="8" t="n"/>
@@ -4279,11 +4279,11 @@
       <c r="A192" s="5" t="n"/>
       <c r="B192" s="5" t="n"/>
       <c r="C192" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B192,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B192,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D192" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B192,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B192,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E192" s="8" t="n"/>
@@ -4298,11 +4298,11 @@
       <c r="A193" s="5" t="n"/>
       <c r="B193" s="5" t="n"/>
       <c r="C193" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B193,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B193,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D193" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B193,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B193,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E193" s="8" t="n"/>
@@ -4317,11 +4317,11 @@
       <c r="A194" s="5" t="n"/>
       <c r="B194" s="5" t="n"/>
       <c r="C194" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B194,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B194,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D194" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B194,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B194,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E194" s="8" t="n"/>
@@ -4336,11 +4336,11 @@
       <c r="A195" s="5" t="n"/>
       <c r="B195" s="5" t="n"/>
       <c r="C195" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B195,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B195,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D195" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B195,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B195,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E195" s="8" t="n"/>
@@ -4355,11 +4355,11 @@
       <c r="A196" s="5" t="n"/>
       <c r="B196" s="5" t="n"/>
       <c r="C196" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B196,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B196,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D196" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B196,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B196,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E196" s="8" t="n"/>
@@ -4374,11 +4374,11 @@
       <c r="A197" s="5" t="n"/>
       <c r="B197" s="5" t="n"/>
       <c r="C197" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B197,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B197,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D197" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B197,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B197,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E197" s="8" t="n"/>
@@ -4393,11 +4393,11 @@
       <c r="A198" s="5" t="n"/>
       <c r="B198" s="5" t="n"/>
       <c r="C198" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B198,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B198,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D198" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B198,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B198,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E198" s="8" t="n"/>
@@ -4412,11 +4412,11 @@
       <c r="A199" s="5" t="n"/>
       <c r="B199" s="5" t="n"/>
       <c r="C199" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B199,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B199,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D199" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B199,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B199,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E199" s="8" t="n"/>
@@ -4431,11 +4431,11 @@
       <c r="A200" s="5" t="n"/>
       <c r="B200" s="5" t="n"/>
       <c r="C200" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B200,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B200,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D200" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B200,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B200,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E200" s="8" t="n"/>
@@ -4450,11 +4450,11 @@
       <c r="A201" s="5" t="n"/>
       <c r="B201" s="5" t="n"/>
       <c r="C201" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B201,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B201,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D201" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B201,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B201,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E201" s="8" t="n"/>
@@ -4469,11 +4469,11 @@
       <c r="A202" s="5" t="n"/>
       <c r="B202" s="5" t="n"/>
       <c r="C202" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B202,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B202,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D202" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B202,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B202,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E202" s="8" t="n"/>
@@ -4488,11 +4488,11 @@
       <c r="A203" s="5" t="n"/>
       <c r="B203" s="5" t="n"/>
       <c r="C203" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B203,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B203,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D203" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B203,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B203,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E203" s="8" t="n"/>
@@ -4507,11 +4507,11 @@
       <c r="A204" s="5" t="n"/>
       <c r="B204" s="5" t="n"/>
       <c r="C204" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B204,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B204,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D204" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B204,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B204,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E204" s="8" t="n"/>
@@ -4526,11 +4526,11 @@
       <c r="A205" s="5" t="n"/>
       <c r="B205" s="5" t="n"/>
       <c r="C205" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B205,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B205,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D205" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B205,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B205,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E205" s="8" t="n"/>
@@ -4545,11 +4545,11 @@
       <c r="A206" s="5" t="n"/>
       <c r="B206" s="5" t="n"/>
       <c r="C206" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B206,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B206,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D206" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B206,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B206,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E206" s="8" t="n"/>
@@ -4564,11 +4564,11 @@
       <c r="A207" s="5" t="n"/>
       <c r="B207" s="5" t="n"/>
       <c r="C207" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B207,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B207,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D207" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B207,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B207,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E207" s="8" t="n"/>
@@ -4583,11 +4583,11 @@
       <c r="A208" s="5" t="n"/>
       <c r="B208" s="5" t="n"/>
       <c r="C208" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B208,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B208,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D208" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B208,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B208,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E208" s="8" t="n"/>
@@ -4602,11 +4602,11 @@
       <c r="A209" s="5" t="n"/>
       <c r="B209" s="5" t="n"/>
       <c r="C209" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B209,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B209,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D209" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B209,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B209,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E209" s="8" t="n"/>
@@ -4621,11 +4621,11 @@
       <c r="A210" s="5" t="n"/>
       <c r="B210" s="5" t="n"/>
       <c r="C210" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B210,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B210,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D210" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B210,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B210,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E210" s="8" t="n"/>
@@ -4640,11 +4640,11 @@
       <c r="A211" s="5" t="n"/>
       <c r="B211" s="5" t="n"/>
       <c r="C211" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B211,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B211,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D211" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B211,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B211,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E211" s="8" t="n"/>
@@ -4659,11 +4659,11 @@
       <c r="A212" s="5" t="n"/>
       <c r="B212" s="5" t="n"/>
       <c r="C212" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B212,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B212,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D212" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B212,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B212,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E212" s="8" t="n"/>
@@ -4678,11 +4678,11 @@
       <c r="A213" s="5" t="n"/>
       <c r="B213" s="5" t="n"/>
       <c r="C213" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B213,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B213,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D213" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B213,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B213,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E213" s="8" t="n"/>
@@ -4697,11 +4697,11 @@
       <c r="A214" s="5" t="n"/>
       <c r="B214" s="5" t="n"/>
       <c r="C214" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B214,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B214,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D214" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B214,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B214,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E214" s="8" t="n"/>
@@ -4716,11 +4716,11 @@
       <c r="A215" s="5" t="n"/>
       <c r="B215" s="5" t="n"/>
       <c r="C215" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B215,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B215,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D215" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B215,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B215,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E215" s="8" t="n"/>
@@ -4735,11 +4735,11 @@
       <c r="A216" s="5" t="n"/>
       <c r="B216" s="5" t="n"/>
       <c r="C216" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B216,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B216,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D216" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B216,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B216,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E216" s="8" t="n"/>
@@ -4754,11 +4754,11 @@
       <c r="A217" s="5" t="n"/>
       <c r="B217" s="5" t="n"/>
       <c r="C217" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B217,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B217,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D217" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B217,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B217,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E217" s="8" t="n"/>
@@ -4773,11 +4773,11 @@
       <c r="A218" s="5" t="n"/>
       <c r="B218" s="5" t="n"/>
       <c r="C218" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B218,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B218,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D218" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B218,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B218,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E218" s="8" t="n"/>
@@ -4792,11 +4792,11 @@
       <c r="A219" s="5" t="n"/>
       <c r="B219" s="5" t="n"/>
       <c r="C219" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B219,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B219,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D219" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B219,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B219,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E219" s="8" t="n"/>
@@ -4811,11 +4811,11 @@
       <c r="A220" s="5" t="n"/>
       <c r="B220" s="5" t="n"/>
       <c r="C220" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B220,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B220,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D220" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B220,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B220,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E220" s="8" t="n"/>
@@ -4830,11 +4830,11 @@
       <c r="A221" s="5" t="n"/>
       <c r="B221" s="5" t="n"/>
       <c r="C221" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B221,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B221,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D221" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B221,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B221,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E221" s="8" t="n"/>
@@ -4849,11 +4849,11 @@
       <c r="A222" s="5" t="n"/>
       <c r="B222" s="5" t="n"/>
       <c r="C222" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B222,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B222,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D222" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B222,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B222,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E222" s="8" t="n"/>
@@ -4868,11 +4868,11 @@
       <c r="A223" s="5" t="n"/>
       <c r="B223" s="5" t="n"/>
       <c r="C223" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B223,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B223,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D223" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B223,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B223,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E223" s="8" t="n"/>
@@ -4887,11 +4887,11 @@
       <c r="A224" s="5" t="n"/>
       <c r="B224" s="5" t="n"/>
       <c r="C224" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B224,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B224,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D224" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B224,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B224,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E224" s="8" t="n"/>
@@ -4906,11 +4906,11 @@
       <c r="A225" s="5" t="n"/>
       <c r="B225" s="5" t="n"/>
       <c r="C225" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B225,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B225,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D225" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B225,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B225,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E225" s="8" t="n"/>
@@ -4925,11 +4925,11 @@
       <c r="A226" s="5" t="n"/>
       <c r="B226" s="5" t="n"/>
       <c r="C226" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B226,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B226,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D226" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B226,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B226,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E226" s="8" t="n"/>
@@ -4944,11 +4944,11 @@
       <c r="A227" s="5" t="n"/>
       <c r="B227" s="5" t="n"/>
       <c r="C227" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B227,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B227,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D227" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B227,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B227,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E227" s="8" t="n"/>
@@ -4963,11 +4963,11 @@
       <c r="A228" s="5" t="n"/>
       <c r="B228" s="5" t="n"/>
       <c r="C228" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B228,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B228,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D228" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B228,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B228,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E228" s="8" t="n"/>
@@ -4982,11 +4982,11 @@
       <c r="A229" s="5" t="n"/>
       <c r="B229" s="5" t="n"/>
       <c r="C229" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B229,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B229,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D229" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B229,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B229,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E229" s="8" t="n"/>
@@ -5001,11 +5001,11 @@
       <c r="A230" s="5" t="n"/>
       <c r="B230" s="5" t="n"/>
       <c r="C230" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B230,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B230,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D230" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B230,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B230,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E230" s="8" t="n"/>
@@ -5020,11 +5020,11 @@
       <c r="A231" s="5" t="n"/>
       <c r="B231" s="5" t="n"/>
       <c r="C231" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B231,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B231,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D231" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B231,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B231,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E231" s="8" t="n"/>
@@ -5039,11 +5039,11 @@
       <c r="A232" s="5" t="n"/>
       <c r="B232" s="5" t="n"/>
       <c r="C232" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B232,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B232,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D232" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B232,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B232,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E232" s="8" t="n"/>
@@ -5058,11 +5058,11 @@
       <c r="A233" s="5" t="n"/>
       <c r="B233" s="5" t="n"/>
       <c r="C233" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B233,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B233,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D233" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B233,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B233,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E233" s="8" t="n"/>
@@ -5077,11 +5077,11 @@
       <c r="A234" s="5" t="n"/>
       <c r="B234" s="5" t="n"/>
       <c r="C234" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B234,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B234,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D234" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B234,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B234,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E234" s="8" t="n"/>
@@ -5096,11 +5096,11 @@
       <c r="A235" s="5" t="n"/>
       <c r="B235" s="5" t="n"/>
       <c r="C235" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B235,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B235,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D235" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B235,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B235,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E235" s="8" t="n"/>
@@ -5115,11 +5115,11 @@
       <c r="A236" s="5" t="n"/>
       <c r="B236" s="5" t="n"/>
       <c r="C236" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B236,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B236,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D236" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B236,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B236,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E236" s="8" t="n"/>
@@ -5134,11 +5134,11 @@
       <c r="A237" s="5" t="n"/>
       <c r="B237" s="5" t="n"/>
       <c r="C237" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B237,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B237,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D237" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B237,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B237,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E237" s="8" t="n"/>
@@ -5153,11 +5153,11 @@
       <c r="A238" s="5" t="n"/>
       <c r="B238" s="5" t="n"/>
       <c r="C238" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B238,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B238,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D238" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B238,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B238,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E238" s="8" t="n"/>
@@ -5172,11 +5172,11 @@
       <c r="A239" s="5" t="n"/>
       <c r="B239" s="5" t="n"/>
       <c r="C239" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B239,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B239,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D239" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B239,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B239,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E239" s="8" t="n"/>
@@ -5191,11 +5191,11 @@
       <c r="A240" s="5" t="n"/>
       <c r="B240" s="5" t="n"/>
       <c r="C240" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B240,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B240,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D240" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B240,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B240,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E240" s="8" t="n"/>
@@ -5210,11 +5210,11 @@
       <c r="A241" s="5" t="n"/>
       <c r="B241" s="5" t="n"/>
       <c r="C241" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B241,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B241,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D241" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B241,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B241,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E241" s="8" t="n"/>
@@ -5229,11 +5229,11 @@
       <c r="A242" s="5" t="n"/>
       <c r="B242" s="5" t="n"/>
       <c r="C242" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B242,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B242,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D242" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B242,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B242,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E242" s="8" t="n"/>
@@ -5248,11 +5248,11 @@
       <c r="A243" s="5" t="n"/>
       <c r="B243" s="5" t="n"/>
       <c r="C243" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B243,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B243,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D243" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B243,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B243,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E243" s="8" t="n"/>
@@ -5267,11 +5267,11 @@
       <c r="A244" s="5" t="n"/>
       <c r="B244" s="5" t="n"/>
       <c r="C244" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B244,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B244,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D244" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B244,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B244,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E244" s="8" t="n"/>
@@ -5286,11 +5286,11 @@
       <c r="A245" s="5" t="n"/>
       <c r="B245" s="5" t="n"/>
       <c r="C245" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B245,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B245,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D245" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B245,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B245,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E245" s="8" t="n"/>
@@ -5305,11 +5305,11 @@
       <c r="A246" s="5" t="n"/>
       <c r="B246" s="5" t="n"/>
       <c r="C246" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B246,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B246,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D246" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B246,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B246,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E246" s="8" t="n"/>
@@ -5324,11 +5324,11 @@
       <c r="A247" s="5" t="n"/>
       <c r="B247" s="5" t="n"/>
       <c r="C247" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B247,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B247,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D247" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B247,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B247,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E247" s="8" t="n"/>
@@ -5343,11 +5343,11 @@
       <c r="A248" s="5" t="n"/>
       <c r="B248" s="5" t="n"/>
       <c r="C248" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B248,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B248,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D248" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B248,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B248,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E248" s="8" t="n"/>
@@ -5362,11 +5362,11 @@
       <c r="A249" s="5" t="n"/>
       <c r="B249" s="5" t="n"/>
       <c r="C249" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B249,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B249,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D249" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B249,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B249,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E249" s="8" t="n"/>
@@ -5381,11 +5381,11 @@
       <c r="A250" s="5" t="n"/>
       <c r="B250" s="5" t="n"/>
       <c r="C250" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B250,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B250,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D250" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B250,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B250,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E250" s="8" t="n"/>
@@ -5400,11 +5400,11 @@
       <c r="A251" s="5" t="n"/>
       <c r="B251" s="5" t="n"/>
       <c r="C251" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B251,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B251,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D251" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B251,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B251,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E251" s="8" t="n"/>
@@ -5419,11 +5419,11 @@
       <c r="A252" s="5" t="n"/>
       <c r="B252" s="5" t="n"/>
       <c r="C252" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B252,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B252,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D252" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B252,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B252,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E252" s="8" t="n"/>
@@ -5438,11 +5438,11 @@
       <c r="A253" s="5" t="n"/>
       <c r="B253" s="5" t="n"/>
       <c r="C253" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B253,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B253,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D253" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B253,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B253,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E253" s="8" t="n"/>
@@ -5457,11 +5457,11 @@
       <c r="A254" s="5" t="n"/>
       <c r="B254" s="5" t="n"/>
       <c r="C254" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B254,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B254,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D254" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B254,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B254,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E254" s="8" t="n"/>
@@ -5476,11 +5476,11 @@
       <c r="A255" s="5" t="n"/>
       <c r="B255" s="5" t="n"/>
       <c r="C255" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B255,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B255,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D255" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B255,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B255,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E255" s="8" t="n"/>
@@ -5495,11 +5495,11 @@
       <c r="A256" s="5" t="n"/>
       <c r="B256" s="5" t="n"/>
       <c r="C256" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B256,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B256,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D256" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B256,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B256,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E256" s="8" t="n"/>
@@ -5514,11 +5514,11 @@
       <c r="A257" s="5" t="n"/>
       <c r="B257" s="5" t="n"/>
       <c r="C257" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B257,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B257,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D257" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B257,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B257,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E257" s="8" t="n"/>
@@ -5533,11 +5533,11 @@
       <c r="A258" s="5" t="n"/>
       <c r="B258" s="5" t="n"/>
       <c r="C258" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B258,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B258,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D258" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B258,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B258,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E258" s="8" t="n"/>
@@ -5552,11 +5552,11 @@
       <c r="A259" s="5" t="n"/>
       <c r="B259" s="5" t="n"/>
       <c r="C259" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B259,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B259,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D259" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B259,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B259,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E259" s="8" t="n"/>
@@ -5571,11 +5571,11 @@
       <c r="A260" s="5" t="n"/>
       <c r="B260" s="5" t="n"/>
       <c r="C260" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B260,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B260,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D260" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B260,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B260,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E260" s="8" t="n"/>
@@ -5590,11 +5590,11 @@
       <c r="A261" s="5" t="n"/>
       <c r="B261" s="5" t="n"/>
       <c r="C261" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B261,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B261,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D261" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B261,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B261,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E261" s="8" t="n"/>
@@ -5609,11 +5609,11 @@
       <c r="A262" s="5" t="n"/>
       <c r="B262" s="5" t="n"/>
       <c r="C262" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B262,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B262,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D262" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B262,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B262,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E262" s="8" t="n"/>
@@ -5628,11 +5628,11 @@
       <c r="A263" s="5" t="n"/>
       <c r="B263" s="5" t="n"/>
       <c r="C263" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B263,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B263,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D263" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B263,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B263,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E263" s="8" t="n"/>
@@ -5647,11 +5647,11 @@
       <c r="A264" s="5" t="n"/>
       <c r="B264" s="5" t="n"/>
       <c r="C264" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B264,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B264,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D264" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B264,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B264,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E264" s="8" t="n"/>
@@ -5666,11 +5666,11 @@
       <c r="A265" s="5" t="n"/>
       <c r="B265" s="5" t="n"/>
       <c r="C265" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B265,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B265,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D265" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B265,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B265,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E265" s="8" t="n"/>
@@ -5685,11 +5685,11 @@
       <c r="A266" s="5" t="n"/>
       <c r="B266" s="5" t="n"/>
       <c r="C266" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B266,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B266,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D266" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B266,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B266,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E266" s="8" t="n"/>
@@ -5704,11 +5704,11 @@
       <c r="A267" s="5" t="n"/>
       <c r="B267" s="5" t="n"/>
       <c r="C267" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B267,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B267,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D267" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B267,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B267,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E267" s="8" t="n"/>
@@ -5723,11 +5723,11 @@
       <c r="A268" s="5" t="n"/>
       <c r="B268" s="5" t="n"/>
       <c r="C268" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B268,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B268,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D268" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B268,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B268,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E268" s="8" t="n"/>
@@ -5742,11 +5742,11 @@
       <c r="A269" s="5" t="n"/>
       <c r="B269" s="5" t="n"/>
       <c r="C269" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B269,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B269,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D269" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B269,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B269,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E269" s="8" t="n"/>
@@ -5761,11 +5761,11 @@
       <c r="A270" s="5" t="n"/>
       <c r="B270" s="5" t="n"/>
       <c r="C270" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B270,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B270,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D270" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B270,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B270,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E270" s="8" t="n"/>
@@ -5780,11 +5780,11 @@
       <c r="A271" s="5" t="n"/>
       <c r="B271" s="5" t="n"/>
       <c r="C271" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B271,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B271,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D271" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B271,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B271,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E271" s="8" t="n"/>
@@ -5799,11 +5799,11 @@
       <c r="A272" s="5" t="n"/>
       <c r="B272" s="5" t="n"/>
       <c r="C272" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B272,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B272,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D272" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B272,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B272,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E272" s="8" t="n"/>
@@ -5818,11 +5818,11 @@
       <c r="A273" s="5" t="n"/>
       <c r="B273" s="5" t="n"/>
       <c r="C273" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B273,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B273,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D273" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B273,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B273,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E273" s="8" t="n"/>
@@ -5837,11 +5837,11 @@
       <c r="A274" s="5" t="n"/>
       <c r="B274" s="5" t="n"/>
       <c r="C274" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B274,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B274,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D274" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B274,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B274,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E274" s="8" t="n"/>
@@ -5856,11 +5856,11 @@
       <c r="A275" s="5" t="n"/>
       <c r="B275" s="5" t="n"/>
       <c r="C275" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B275,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B275,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D275" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B275,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B275,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E275" s="8" t="n"/>
@@ -5875,11 +5875,11 @@
       <c r="A276" s="5" t="n"/>
       <c r="B276" s="5" t="n"/>
       <c r="C276" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B276,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B276,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D276" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B276,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B276,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E276" s="8" t="n"/>
@@ -5894,11 +5894,11 @@
       <c r="A277" s="5" t="n"/>
       <c r="B277" s="5" t="n"/>
       <c r="C277" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B277,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B277,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D277" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B277,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B277,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E277" s="8" t="n"/>
@@ -5913,11 +5913,11 @@
       <c r="A278" s="5" t="n"/>
       <c r="B278" s="5" t="n"/>
       <c r="C278" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B278,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B278,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D278" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B278,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B278,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E278" s="8" t="n"/>
@@ -5932,11 +5932,11 @@
       <c r="A279" s="5" t="n"/>
       <c r="B279" s="5" t="n"/>
       <c r="C279" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B279,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B279,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D279" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B279,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B279,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E279" s="8" t="n"/>
@@ -5951,11 +5951,11 @@
       <c r="A280" s="5" t="n"/>
       <c r="B280" s="5" t="n"/>
       <c r="C280" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B280,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B280,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D280" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B280,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B280,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E280" s="8" t="n"/>
@@ -5970,11 +5970,11 @@
       <c r="A281" s="5" t="n"/>
       <c r="B281" s="5" t="n"/>
       <c r="C281" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B281,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B281,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D281" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B281,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B281,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E281" s="8" t="n"/>
@@ -5989,11 +5989,11 @@
       <c r="A282" s="5" t="n"/>
       <c r="B282" s="5" t="n"/>
       <c r="C282" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B282,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B282,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D282" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B282,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B282,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E282" s="8" t="n"/>
@@ -6008,11 +6008,11 @@
       <c r="A283" s="5" t="n"/>
       <c r="B283" s="5" t="n"/>
       <c r="C283" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B283,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B283,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D283" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B283,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B283,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E283" s="8" t="n"/>
@@ -6027,11 +6027,11 @@
       <c r="A284" s="5" t="n"/>
       <c r="B284" s="5" t="n"/>
       <c r="C284" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B284,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B284,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D284" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B284,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B284,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E284" s="8" t="n"/>
@@ -6046,11 +6046,11 @@
       <c r="A285" s="5" t="n"/>
       <c r="B285" s="5" t="n"/>
       <c r="C285" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B285,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B285,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D285" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B285,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B285,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E285" s="8" t="n"/>
@@ -6065,11 +6065,11 @@
       <c r="A286" s="5" t="n"/>
       <c r="B286" s="5" t="n"/>
       <c r="C286" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B286,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B286,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D286" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B286,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B286,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E286" s="8" t="n"/>
@@ -6084,11 +6084,11 @@
       <c r="A287" s="5" t="n"/>
       <c r="B287" s="5" t="n"/>
       <c r="C287" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B287,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B287,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D287" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B287,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B287,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E287" s="8" t="n"/>
@@ -6103,11 +6103,11 @@
       <c r="A288" s="5" t="n"/>
       <c r="B288" s="5" t="n"/>
       <c r="C288" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B288,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B288,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D288" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B288,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B288,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E288" s="8" t="n"/>
@@ -6122,11 +6122,11 @@
       <c r="A289" s="5" t="n"/>
       <c r="B289" s="5" t="n"/>
       <c r="C289" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B289,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B289,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D289" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B289,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B289,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E289" s="8" t="n"/>
@@ -6141,11 +6141,11 @@
       <c r="A290" s="5" t="n"/>
       <c r="B290" s="5" t="n"/>
       <c r="C290" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B290,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B290,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D290" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B290,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B290,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E290" s="8" t="n"/>
@@ -6160,11 +6160,11 @@
       <c r="A291" s="5" t="n"/>
       <c r="B291" s="5" t="n"/>
       <c r="C291" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B291,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B291,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D291" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B291,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B291,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E291" s="8" t="n"/>
@@ -6179,11 +6179,11 @@
       <c r="A292" s="5" t="n"/>
       <c r="B292" s="5" t="n"/>
       <c r="C292" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B292,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B292,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D292" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B292,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B292,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E292" s="8" t="n"/>
@@ -6198,11 +6198,11 @@
       <c r="A293" s="5" t="n"/>
       <c r="B293" s="5" t="n"/>
       <c r="C293" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B293,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B293,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D293" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B293,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B293,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E293" s="8" t="n"/>
@@ -6217,11 +6217,11 @@
       <c r="A294" s="5" t="n"/>
       <c r="B294" s="5" t="n"/>
       <c r="C294" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B294,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B294,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D294" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B294,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B294,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E294" s="8" t="n"/>
@@ -6236,11 +6236,11 @@
       <c r="A295" s="5" t="n"/>
       <c r="B295" s="5" t="n"/>
       <c r="C295" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B295,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B295,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D295" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B295,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B295,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E295" s="8" t="n"/>
@@ -6255,11 +6255,11 @@
       <c r="A296" s="5" t="n"/>
       <c r="B296" s="5" t="n"/>
       <c r="C296" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B296,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B296,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D296" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B296,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B296,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E296" s="8" t="n"/>
@@ -6274,11 +6274,11 @@
       <c r="A297" s="5" t="n"/>
       <c r="B297" s="5" t="n"/>
       <c r="C297" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B297,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B297,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D297" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B297,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B297,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E297" s="8" t="n"/>
@@ -6293,11 +6293,11 @@
       <c r="A298" s="5" t="n"/>
       <c r="B298" s="5" t="n"/>
       <c r="C298" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B298,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B298,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D298" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B298,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B298,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E298" s="8" t="n"/>
@@ -6312,11 +6312,11 @@
       <c r="A299" s="5" t="n"/>
       <c r="B299" s="5" t="n"/>
       <c r="C299" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B299,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B299,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D299" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B299,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B299,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E299" s="8" t="n"/>
@@ -6331,11 +6331,11 @@
       <c r="A300" s="5" t="n"/>
       <c r="B300" s="5" t="n"/>
       <c r="C300" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B300,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B300,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D300" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B300,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B300,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E300" s="8" t="n"/>
@@ -6350,11 +6350,11 @@
       <c r="A301" s="5" t="n"/>
       <c r="B301" s="5" t="n"/>
       <c r="C301" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B301,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B301,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D301" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B301,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B301,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E301" s="8" t="n"/>
@@ -6369,11 +6369,11 @@
       <c r="A302" s="5" t="n"/>
       <c r="B302" s="5" t="n"/>
       <c r="C302" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B302,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B302,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D302" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B302,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B302,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E302" s="8" t="n"/>
@@ -6388,11 +6388,11 @@
       <c r="A303" s="5" t="n"/>
       <c r="B303" s="5" t="n"/>
       <c r="C303" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B303,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B303,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D303" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B303,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B303,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E303" s="8" t="n"/>
@@ -6407,11 +6407,11 @@
       <c r="A304" s="5" t="n"/>
       <c r="B304" s="5" t="n"/>
       <c r="C304" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B304,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B304,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D304" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B304,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B304,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E304" s="8" t="n"/>
@@ -6426,11 +6426,11 @@
       <c r="A305" s="5" t="n"/>
       <c r="B305" s="5" t="n"/>
       <c r="C305" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B305,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B305,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D305" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B305,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B305,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E305" s="8" t="n"/>
@@ -6445,11 +6445,11 @@
       <c r="A306" s="5" t="n"/>
       <c r="B306" s="5" t="n"/>
       <c r="C306" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B306,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B306,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D306" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B306,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B306,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E306" s="8" t="n"/>
@@ -6464,11 +6464,11 @@
       <c r="A307" s="5" t="n"/>
       <c r="B307" s="5" t="n"/>
       <c r="C307" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B307,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B307,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D307" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B307,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B307,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E307" s="8" t="n"/>
@@ -6483,11 +6483,11 @@
       <c r="A308" s="5" t="n"/>
       <c r="B308" s="5" t="n"/>
       <c r="C308" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B308,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B308,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D308" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B308,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B308,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E308" s="8" t="n"/>
@@ -6502,11 +6502,11 @@
       <c r="A309" s="5" t="n"/>
       <c r="B309" s="5" t="n"/>
       <c r="C309" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B309,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B309,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D309" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B309,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B309,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E309" s="8" t="n"/>
@@ -6521,11 +6521,11 @@
       <c r="A310" s="5" t="n"/>
       <c r="B310" s="5" t="n"/>
       <c r="C310" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B310,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B310,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D310" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B310,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B310,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E310" s="8" t="n"/>
@@ -6540,11 +6540,11 @@
       <c r="A311" s="5" t="n"/>
       <c r="B311" s="5" t="n"/>
       <c r="C311" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B311,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B311,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D311" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B311,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B311,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E311" s="8" t="n"/>
@@ -6559,11 +6559,11 @@
       <c r="A312" s="5" t="n"/>
       <c r="B312" s="5" t="n"/>
       <c r="C312" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B312,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B312,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D312" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B312,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B312,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E312" s="8" t="n"/>
@@ -6578,11 +6578,11 @@
       <c r="A313" s="5" t="n"/>
       <c r="B313" s="5" t="n"/>
       <c r="C313" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B313,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B313,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D313" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B313,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B313,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E313" s="8" t="n"/>
@@ -6597,11 +6597,11 @@
       <c r="A314" s="5" t="n"/>
       <c r="B314" s="5" t="n"/>
       <c r="C314" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B314,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B314,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D314" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B314,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B314,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E314" s="8" t="n"/>
@@ -6616,11 +6616,11 @@
       <c r="A315" s="5" t="n"/>
       <c r="B315" s="5" t="n"/>
       <c r="C315" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B315,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B315,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D315" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B315,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B315,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E315" s="8" t="n"/>
@@ -6635,11 +6635,11 @@
       <c r="A316" s="5" t="n"/>
       <c r="B316" s="5" t="n"/>
       <c r="C316" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B316,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B316,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D316" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B316,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B316,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E316" s="8" t="n"/>
@@ -6654,11 +6654,11 @@
       <c r="A317" s="5" t="n"/>
       <c r="B317" s="5" t="n"/>
       <c r="C317" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B317,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B317,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D317" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B317,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B317,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E317" s="8" t="n"/>
@@ -6673,11 +6673,11 @@
       <c r="A318" s="5" t="n"/>
       <c r="B318" s="5" t="n"/>
       <c r="C318" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B318,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B318,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D318" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B318,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B318,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E318" s="8" t="n"/>
@@ -6692,11 +6692,11 @@
       <c r="A319" s="5" t="n"/>
       <c r="B319" s="5" t="n"/>
       <c r="C319" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B319,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B319,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D319" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B319,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B319,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E319" s="8" t="n"/>
@@ -6711,11 +6711,11 @@
       <c r="A320" s="5" t="n"/>
       <c r="B320" s="5" t="n"/>
       <c r="C320" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B320,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B320,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D320" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B320,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B320,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E320" s="8" t="n"/>
@@ -6730,11 +6730,11 @@
       <c r="A321" s="5" t="n"/>
       <c r="B321" s="5" t="n"/>
       <c r="C321" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B321,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B321,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D321" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B321,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B321,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E321" s="8" t="n"/>
@@ -6749,11 +6749,11 @@
       <c r="A322" s="5" t="n"/>
       <c r="B322" s="5" t="n"/>
       <c r="C322" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B322,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B322,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D322" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B322,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B322,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E322" s="8" t="n"/>
@@ -6768,11 +6768,11 @@
       <c r="A323" s="5" t="n"/>
       <c r="B323" s="5" t="n"/>
       <c r="C323" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B323,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B323,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D323" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B323,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B323,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E323" s="8" t="n"/>
@@ -6787,11 +6787,11 @@
       <c r="A324" s="5" t="n"/>
       <c r="B324" s="5" t="n"/>
       <c r="C324" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B324,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B324,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D324" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B324,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B324,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E324" s="8" t="n"/>
@@ -6806,11 +6806,11 @@
       <c r="A325" s="5" t="n"/>
       <c r="B325" s="5" t="n"/>
       <c r="C325" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B325,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B325,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D325" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B325,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B325,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E325" s="8" t="n"/>
@@ -6825,11 +6825,11 @@
       <c r="A326" s="5" t="n"/>
       <c r="B326" s="5" t="n"/>
       <c r="C326" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B326,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B326,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D326" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B326,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B326,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E326" s="8" t="n"/>
@@ -6844,11 +6844,11 @@
       <c r="A327" s="5" t="n"/>
       <c r="B327" s="5" t="n"/>
       <c r="C327" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B327,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B327,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D327" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B327,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B327,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E327" s="8" t="n"/>
@@ -6863,11 +6863,11 @@
       <c r="A328" s="5" t="n"/>
       <c r="B328" s="5" t="n"/>
       <c r="C328" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B328,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B328,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D328" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B328,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B328,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E328" s="8" t="n"/>
@@ -6882,11 +6882,11 @@
       <c r="A329" s="5" t="n"/>
       <c r="B329" s="5" t="n"/>
       <c r="C329" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B329,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B329,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D329" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B329,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B329,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E329" s="8" t="n"/>
@@ -6901,11 +6901,11 @@
       <c r="A330" s="5" t="n"/>
       <c r="B330" s="5" t="n"/>
       <c r="C330" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B330,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B330,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D330" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B330,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B330,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E330" s="8" t="n"/>
@@ -6920,11 +6920,11 @@
       <c r="A331" s="5" t="n"/>
       <c r="B331" s="5" t="n"/>
       <c r="C331" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B331,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B331,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D331" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B331,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B331,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E331" s="8" t="n"/>
@@ -6939,11 +6939,11 @@
       <c r="A332" s="5" t="n"/>
       <c r="B332" s="5" t="n"/>
       <c r="C332" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B332,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B332,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D332" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B332,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B332,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E332" s="8" t="n"/>
@@ -6958,11 +6958,11 @@
       <c r="A333" s="5" t="n"/>
       <c r="B333" s="5" t="n"/>
       <c r="C333" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B333,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B333,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D333" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B333,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B333,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E333" s="8" t="n"/>
@@ -6977,11 +6977,11 @@
       <c r="A334" s="5" t="n"/>
       <c r="B334" s="5" t="n"/>
       <c r="C334" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B334,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B334,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D334" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B334,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B334,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E334" s="8" t="n"/>
@@ -6996,11 +6996,11 @@
       <c r="A335" s="5" t="n"/>
       <c r="B335" s="5" t="n"/>
       <c r="C335" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B335,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B335,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D335" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B335,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B335,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E335" s="8" t="n"/>
@@ -7015,11 +7015,11 @@
       <c r="A336" s="5" t="n"/>
       <c r="B336" s="5" t="n"/>
       <c r="C336" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B336,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B336,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D336" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B336,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B336,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E336" s="8" t="n"/>
@@ -7034,11 +7034,11 @@
       <c r="A337" s="5" t="n"/>
       <c r="B337" s="5" t="n"/>
       <c r="C337" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B337,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B337,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D337" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B337,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B337,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E337" s="8" t="n"/>
@@ -7053,11 +7053,11 @@
       <c r="A338" s="5" t="n"/>
       <c r="B338" s="5" t="n"/>
       <c r="C338" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B338,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B338,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D338" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B338,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B338,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E338" s="8" t="n"/>
@@ -7072,11 +7072,11 @@
       <c r="A339" s="5" t="n"/>
       <c r="B339" s="5" t="n"/>
       <c r="C339" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B339,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B339,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D339" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B339,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B339,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E339" s="8" t="n"/>
@@ -7091,11 +7091,11 @@
       <c r="A340" s="5" t="n"/>
       <c r="B340" s="5" t="n"/>
       <c r="C340" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B340,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B340,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D340" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B340,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B340,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E340" s="8" t="n"/>
@@ -7110,11 +7110,11 @@
       <c r="A341" s="5" t="n"/>
       <c r="B341" s="5" t="n"/>
       <c r="C341" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B341,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B341,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D341" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B341,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B341,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E341" s="8" t="n"/>
@@ -7129,11 +7129,11 @@
       <c r="A342" s="5" t="n"/>
       <c r="B342" s="5" t="n"/>
       <c r="C342" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B342,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B342,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D342" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B342,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B342,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E342" s="8" t="n"/>
@@ -7148,11 +7148,11 @@
       <c r="A343" s="5" t="n"/>
       <c r="B343" s="5" t="n"/>
       <c r="C343" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B343,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B343,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D343" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B343,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B343,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E343" s="8" t="n"/>
@@ -7167,11 +7167,11 @@
       <c r="A344" s="5" t="n"/>
       <c r="B344" s="5" t="n"/>
       <c r="C344" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B344,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B344,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D344" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B344,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B344,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E344" s="8" t="n"/>
@@ -7186,11 +7186,11 @@
       <c r="A345" s="5" t="n"/>
       <c r="B345" s="5" t="n"/>
       <c r="C345" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B345,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B345,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D345" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B345,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B345,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E345" s="8" t="n"/>
@@ -7205,11 +7205,11 @@
       <c r="A346" s="5" t="n"/>
       <c r="B346" s="5" t="n"/>
       <c r="C346" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B346,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B346,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D346" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B346,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B346,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E346" s="8" t="n"/>
@@ -7224,11 +7224,11 @@
       <c r="A347" s="5" t="n"/>
       <c r="B347" s="5" t="n"/>
       <c r="C347" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B347,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B347,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D347" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B347,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B347,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E347" s="8" t="n"/>
@@ -7243,11 +7243,11 @@
       <c r="A348" s="5" t="n"/>
       <c r="B348" s="5" t="n"/>
       <c r="C348" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B348,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B348,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D348" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B348,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B348,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E348" s="8" t="n"/>
@@ -7262,11 +7262,11 @@
       <c r="A349" s="5" t="n"/>
       <c r="B349" s="5" t="n"/>
       <c r="C349" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B349,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B349,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D349" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B349,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B349,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E349" s="8" t="n"/>
@@ -7281,11 +7281,11 @@
       <c r="A350" s="5" t="n"/>
       <c r="B350" s="5" t="n"/>
       <c r="C350" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B350,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B350,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D350" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B350,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B350,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E350" s="8" t="n"/>
@@ -7300,11 +7300,11 @@
       <c r="A351" s="5" t="n"/>
       <c r="B351" s="5" t="n"/>
       <c r="C351" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B351,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B351,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D351" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B351,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B351,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E351" s="8" t="n"/>
@@ -7319,11 +7319,11 @@
       <c r="A352" s="5" t="n"/>
       <c r="B352" s="5" t="n"/>
       <c r="C352" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B352,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B352,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D352" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B352,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B352,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E352" s="8" t="n"/>
@@ -7338,11 +7338,11 @@
       <c r="A353" s="5" t="n"/>
       <c r="B353" s="5" t="n"/>
       <c r="C353" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B353,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B353,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D353" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B353,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B353,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E353" s="8" t="n"/>
@@ -7357,11 +7357,11 @@
       <c r="A354" s="5" t="n"/>
       <c r="B354" s="5" t="n"/>
       <c r="C354" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B354,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B354,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D354" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B354,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B354,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E354" s="8" t="n"/>
@@ -7376,11 +7376,11 @@
       <c r="A355" s="5" t="n"/>
       <c r="B355" s="5" t="n"/>
       <c r="C355" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B355,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B355,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D355" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B355,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B355,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E355" s="8" t="n"/>
@@ -7395,11 +7395,11 @@
       <c r="A356" s="5" t="n"/>
       <c r="B356" s="5" t="n"/>
       <c r="C356" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B356,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B356,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D356" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B356,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B356,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E356" s="8" t="n"/>
@@ -7414,11 +7414,11 @@
       <c r="A357" s="5" t="n"/>
       <c r="B357" s="5" t="n"/>
       <c r="C357" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B357,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B357,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D357" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B357,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B357,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E357" s="8" t="n"/>
@@ -7433,11 +7433,11 @@
       <c r="A358" s="5" t="n"/>
       <c r="B358" s="5" t="n"/>
       <c r="C358" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B358,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B358,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D358" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B358,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B358,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E358" s="8" t="n"/>
@@ -7452,11 +7452,11 @@
       <c r="A359" s="5" t="n"/>
       <c r="B359" s="5" t="n"/>
       <c r="C359" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B359,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B359,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D359" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B359,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B359,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E359" s="8" t="n"/>
@@ -7471,11 +7471,11 @@
       <c r="A360" s="5" t="n"/>
       <c r="B360" s="5" t="n"/>
       <c r="C360" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B360,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B360,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D360" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B360,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B360,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E360" s="8" t="n"/>
@@ -7490,11 +7490,11 @@
       <c r="A361" s="5" t="n"/>
       <c r="B361" s="5" t="n"/>
       <c r="C361" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B361,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B361,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D361" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B361,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B361,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E361" s="8" t="n"/>
@@ -7509,11 +7509,11 @@
       <c r="A362" s="5" t="n"/>
       <c r="B362" s="5" t="n"/>
       <c r="C362" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B362,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B362,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D362" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B362,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B362,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E362" s="8" t="n"/>
@@ -7528,11 +7528,11 @@
       <c r="A363" s="5" t="n"/>
       <c r="B363" s="5" t="n"/>
       <c r="C363" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B363,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B363,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D363" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B363,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B363,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E363" s="8" t="n"/>
@@ -7547,11 +7547,11 @@
       <c r="A364" s="5" t="n"/>
       <c r="B364" s="5" t="n"/>
       <c r="C364" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B364,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B364,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D364" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B364,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B364,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E364" s="8" t="n"/>
@@ -7566,11 +7566,11 @@
       <c r="A365" s="5" t="n"/>
       <c r="B365" s="5" t="n"/>
       <c r="C365" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B365,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B365,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D365" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B365,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B365,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E365" s="8" t="n"/>
@@ -7585,11 +7585,11 @@
       <c r="A366" s="5" t="n"/>
       <c r="B366" s="5" t="n"/>
       <c r="C366" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B366,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B366,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D366" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B366,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B366,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E366" s="8" t="n"/>
@@ -7604,11 +7604,11 @@
       <c r="A367" s="5" t="n"/>
       <c r="B367" s="5" t="n"/>
       <c r="C367" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B367,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B367,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D367" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B367,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B367,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E367" s="8" t="n"/>
@@ -7623,11 +7623,11 @@
       <c r="A368" s="5" t="n"/>
       <c r="B368" s="5" t="n"/>
       <c r="C368" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B368,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B368,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D368" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B368,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B368,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E368" s="8" t="n"/>
@@ -7642,11 +7642,11 @@
       <c r="A369" s="5" t="n"/>
       <c r="B369" s="5" t="n"/>
       <c r="C369" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B369,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B369,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D369" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B369,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B369,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E369" s="8" t="n"/>
@@ -7661,11 +7661,11 @@
       <c r="A370" s="5" t="n"/>
       <c r="B370" s="5" t="n"/>
       <c r="C370" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B370,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B370,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D370" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B370,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B370,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E370" s="8" t="n"/>
@@ -7680,11 +7680,11 @@
       <c r="A371" s="5" t="n"/>
       <c r="B371" s="5" t="n"/>
       <c r="C371" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B371,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B371,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D371" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B371,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B371,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E371" s="8" t="n"/>
@@ -7699,11 +7699,11 @@
       <c r="A372" s="5" t="n"/>
       <c r="B372" s="5" t="n"/>
       <c r="C372" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B372,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B372,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D372" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B372,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B372,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E372" s="8" t="n"/>
@@ -7718,11 +7718,11 @@
       <c r="A373" s="5" t="n"/>
       <c r="B373" s="5" t="n"/>
       <c r="C373" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B373,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B373,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D373" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B373,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B373,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E373" s="8" t="n"/>
@@ -7737,11 +7737,11 @@
       <c r="A374" s="5" t="n"/>
       <c r="B374" s="5" t="n"/>
       <c r="C374" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B374,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B374,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D374" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B374,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B374,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E374" s="8" t="n"/>
@@ -7756,11 +7756,11 @@
       <c r="A375" s="5" t="n"/>
       <c r="B375" s="5" t="n"/>
       <c r="C375" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B375,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B375,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D375" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B375,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B375,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E375" s="8" t="n"/>
@@ -7775,11 +7775,11 @@
       <c r="A376" s="5" t="n"/>
       <c r="B376" s="5" t="n"/>
       <c r="C376" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B376,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B376,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D376" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B376,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B376,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E376" s="8" t="n"/>
@@ -7794,11 +7794,11 @@
       <c r="A377" s="5" t="n"/>
       <c r="B377" s="5" t="n"/>
       <c r="C377" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B377,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B377,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D377" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B377,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B377,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E377" s="8" t="n"/>
@@ -7813,11 +7813,11 @@
       <c r="A378" s="5" t="n"/>
       <c r="B378" s="5" t="n"/>
       <c r="C378" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B378,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B378,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D378" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B378,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B378,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E378" s="8" t="n"/>
@@ -7832,11 +7832,11 @@
       <c r="A379" s="5" t="n"/>
       <c r="B379" s="5" t="n"/>
       <c r="C379" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B379,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B379,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D379" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B379,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B379,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E379" s="8" t="n"/>
@@ -7851,11 +7851,11 @@
       <c r="A380" s="5" t="n"/>
       <c r="B380" s="5" t="n"/>
       <c r="C380" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B380,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B380,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D380" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B380,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B380,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E380" s="8" t="n"/>
@@ -7870,11 +7870,11 @@
       <c r="A381" s="5" t="n"/>
       <c r="B381" s="5" t="n"/>
       <c r="C381" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B381,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B381,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D381" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B381,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B381,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E381" s="8" t="n"/>
@@ -7889,11 +7889,11 @@
       <c r="A382" s="5" t="n"/>
       <c r="B382" s="5" t="n"/>
       <c r="C382" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B382,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B382,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D382" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B382,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B382,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E382" s="8" t="n"/>
@@ -7908,11 +7908,11 @@
       <c r="A383" s="5" t="n"/>
       <c r="B383" s="5" t="n"/>
       <c r="C383" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B383,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B383,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D383" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B383,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B383,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E383" s="8" t="n"/>
@@ -7927,11 +7927,11 @@
       <c r="A384" s="5" t="n"/>
       <c r="B384" s="5" t="n"/>
       <c r="C384" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B384,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B384,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D384" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B384,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B384,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E384" s="8" t="n"/>
@@ -7946,11 +7946,11 @@
       <c r="A385" s="5" t="n"/>
       <c r="B385" s="5" t="n"/>
       <c r="C385" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B385,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B385,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D385" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B385,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B385,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E385" s="8" t="n"/>
@@ -7965,11 +7965,11 @@
       <c r="A386" s="5" t="n"/>
       <c r="B386" s="5" t="n"/>
       <c r="C386" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B386,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B386,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D386" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B386,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B386,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E386" s="8" t="n"/>
@@ -7984,11 +7984,11 @@
       <c r="A387" s="5" t="n"/>
       <c r="B387" s="5" t="n"/>
       <c r="C387" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B387,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B387,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D387" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B387,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B387,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E387" s="8" t="n"/>
@@ -8003,11 +8003,11 @@
       <c r="A388" s="5" t="n"/>
       <c r="B388" s="5" t="n"/>
       <c r="C388" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B388,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B388,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D388" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B388,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B388,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E388" s="8" t="n"/>
@@ -8022,11 +8022,11 @@
       <c r="A389" s="5" t="n"/>
       <c r="B389" s="5" t="n"/>
       <c r="C389" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B389,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B389,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D389" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B389,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B389,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E389" s="8" t="n"/>
@@ -8041,11 +8041,11 @@
       <c r="A390" s="5" t="n"/>
       <c r="B390" s="5" t="n"/>
       <c r="C390" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B390,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B390,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D390" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B390,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B390,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E390" s="8" t="n"/>
@@ -8060,11 +8060,11 @@
       <c r="A391" s="5" t="n"/>
       <c r="B391" s="5" t="n"/>
       <c r="C391" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B391,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B391,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D391" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B391,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B391,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E391" s="8" t="n"/>
@@ -8079,11 +8079,11 @@
       <c r="A392" s="5" t="n"/>
       <c r="B392" s="5" t="n"/>
       <c r="C392" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B392,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B392,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D392" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B392,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B392,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E392" s="8" t="n"/>
@@ -8098,11 +8098,11 @@
       <c r="A393" s="5" t="n"/>
       <c r="B393" s="5" t="n"/>
       <c r="C393" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B393,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B393,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D393" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B393,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B393,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E393" s="8" t="n"/>
@@ -8117,11 +8117,11 @@
       <c r="A394" s="5" t="n"/>
       <c r="B394" s="5" t="n"/>
       <c r="C394" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B394,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B394,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D394" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B394,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B394,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E394" s="8" t="n"/>
@@ -8136,11 +8136,11 @@
       <c r="A395" s="5" t="n"/>
       <c r="B395" s="5" t="n"/>
       <c r="C395" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B395,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B395,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D395" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B395,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B395,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E395" s="8" t="n"/>
@@ -8155,11 +8155,11 @@
       <c r="A396" s="5" t="n"/>
       <c r="B396" s="5" t="n"/>
       <c r="C396" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B396,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B396,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D396" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B396,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B396,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E396" s="8" t="n"/>
@@ -8174,11 +8174,11 @@
       <c r="A397" s="5" t="n"/>
       <c r="B397" s="5" t="n"/>
       <c r="C397" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B397,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B397,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D397" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B397,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B397,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E397" s="8" t="n"/>
@@ -8193,11 +8193,11 @@
       <c r="A398" s="5" t="n"/>
       <c r="B398" s="5" t="n"/>
       <c r="C398" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B398,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B398,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D398" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B398,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B398,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E398" s="8" t="n"/>
@@ -8212,11 +8212,11 @@
       <c r="A399" s="5" t="n"/>
       <c r="B399" s="5" t="n"/>
       <c r="C399" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B399,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B399,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D399" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B399,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B399,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E399" s="8" t="n"/>
@@ -8231,11 +8231,11 @@
       <c r="A400" s="5" t="n"/>
       <c r="B400" s="5" t="n"/>
       <c r="C400" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B400,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B400,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D400" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B400,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B400,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E400" s="8" t="n"/>
@@ -8250,11 +8250,11 @@
       <c r="A401" s="5" t="n"/>
       <c r="B401" s="5" t="n"/>
       <c r="C401" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B401,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B401,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D401" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B401,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B401,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E401" s="8" t="n"/>
@@ -8269,11 +8269,11 @@
       <c r="A402" s="5" t="n"/>
       <c r="B402" s="5" t="n"/>
       <c r="C402" s="6">
-        <f>IFERROR(INDEX(Productos!$B$2:$B$770,MATCH(B402,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$B$2:$B$769,MATCH(B402,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="D402" s="7">
-        <f>IFERROR(INDEX(Productos!$C$2:$C$770,MATCH(B402,Productos!$A$2:$A$770,0)),"")</f>
+        <f>IFERROR(INDEX(Productos!$C$2:$C$769,MATCH(B402,Productos!$A$2:$A$769,0)),"")</f>
         <v/>
       </c>
       <c r="E402" s="8" t="n"/>
@@ -10547,11 +10547,6 @@
           <t>ROYAL CANIN ADULT POODLE 1.5KG · 90401950000</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>SUPRA CACHORRO 4KG · 93508920000</t>
-        </is>
-      </c>
       <c r="BA10" t="inlineStr">
         <is>
           <t>TOW HUMEDALES CANINOS CON AVES SILVESTRE · 90013270000</t>
@@ -13159,7 +13154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D774"/>
+  <dimension ref="A1:D773"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13256,7 +13251,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -13296,7 +13291,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -14256,7 +14251,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -14276,7 +14271,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -14436,7 +14431,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -14476,7 +14471,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -14956,7 +14951,7 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -15356,7 +15351,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -15376,7 +15371,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -15736,7 +15731,7 @@
         </is>
       </c>
       <c r="C129" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15916,7 +15911,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16036,7 +16031,7 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16096,7 +16091,7 @@
         </is>
       </c>
       <c r="C147" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16676,7 +16671,7 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -16696,7 +16691,7 @@
         </is>
       </c>
       <c r="C177" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -17056,7 +17051,7 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -17116,7 +17111,7 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -17576,7 +17571,7 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -18576,7 +18571,7 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19356,7 +19351,7 @@
         </is>
       </c>
       <c r="C310" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -19376,7 +19371,7 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -19516,7 +19511,7 @@
         </is>
       </c>
       <c r="C318" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -19756,7 +19751,7 @@
         </is>
       </c>
       <c r="C330" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -19956,7 +19951,7 @@
         </is>
       </c>
       <c r="C340" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -20056,7 +20051,7 @@
         </is>
       </c>
       <c r="C345" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -20076,7 +20071,7 @@
         </is>
       </c>
       <c r="C346" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -20096,7 +20091,7 @@
         </is>
       </c>
       <c r="C347" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -20276,7 +20271,7 @@
         </is>
       </c>
       <c r="C356" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -20356,7 +20351,7 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -20536,7 +20531,7 @@
         </is>
       </c>
       <c r="C369" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -20696,7 +20691,7 @@
         </is>
       </c>
       <c r="C377" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -21256,7 +21251,7 @@
         </is>
       </c>
       <c r="C405" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -21636,7 +21631,7 @@
         </is>
       </c>
       <c r="C424" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -21876,7 +21871,7 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -21956,7 +21951,7 @@
         </is>
       </c>
       <c r="C440" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -21976,7 +21971,7 @@
         </is>
       </c>
       <c r="C441" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -22296,7 +22291,7 @@
         </is>
       </c>
       <c r="C457" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -23356,7 +23351,7 @@
         </is>
       </c>
       <c r="C510" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -23436,7 +23431,7 @@
         </is>
       </c>
       <c r="C514" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -23536,7 +23531,7 @@
         </is>
       </c>
       <c r="C519" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -23616,7 +23611,7 @@
         </is>
       </c>
       <c r="C523" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -23776,7 +23771,7 @@
         </is>
       </c>
       <c r="C531" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -23816,7 +23811,7 @@
         </is>
       </c>
       <c r="C533" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -24136,7 +24131,7 @@
         </is>
       </c>
       <c r="C549" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -24316,7 +24311,7 @@
         </is>
       </c>
       <c r="C558" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -24396,7 +24391,7 @@
         </is>
       </c>
       <c r="C562" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -24876,7 +24871,7 @@
         </is>
       </c>
       <c r="C586" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -24956,7 +24951,7 @@
         </is>
       </c>
       <c r="C590" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -25116,7 +25111,7 @@
         </is>
       </c>
       <c r="C598" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -25196,7 +25191,7 @@
         </is>
       </c>
       <c r="C602" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -25396,7 +25391,7 @@
         </is>
       </c>
       <c r="C612" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -25536,7 +25531,7 @@
         </is>
       </c>
       <c r="C619" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -26156,7 +26151,7 @@
         </is>
       </c>
       <c r="C650" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -26456,7 +26451,7 @@
         </is>
       </c>
       <c r="C665" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -26867,36 +26862,36 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>SUPRA CACHORRO 4KG · 93508920000</t>
+          <t>SHED-X SUPLEMENTO PERROS GRANDES · 90334000000</t>
         </is>
       </c>
       <c r="B686" t="inlineStr">
         <is>
-          <t>93508920000</t>
+          <t>90334000000</t>
         </is>
       </c>
       <c r="C686" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>SUPRA</t>
+          <t>SYNERGY</t>
         </is>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>SHED-X SUPLEMENTO PERROS GRANDES · 90334000000</t>
+          <t>SHED-X SUPLEMENTO PERROS MEDIANOS · 90333990000</t>
         </is>
       </c>
       <c r="B687" t="inlineStr">
         <is>
-          <t>90334000000</t>
+          <t>90333990000</t>
         </is>
       </c>
       <c r="C687" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -26907,36 +26902,36 @@
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>SHED-X SUPLEMENTO PERROS MEDIANOS · 90333990000</t>
+          <t>TOW ARROYO ANTIGUO CON SALMÓN AHUMADO 2, · 90013320000</t>
         </is>
       </c>
       <c r="B688" t="inlineStr">
         <is>
-          <t>90333990000</t>
+          <t>90013320000</t>
         </is>
       </c>
       <c r="C688" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>SYNERGY</t>
+          <t>TASTE OF THE WILD</t>
         </is>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>TOW ARROYO ANTIGUO CON SALMÓN AHUMADO 2, · 90013320000</t>
+          <t>TOW CAÑÓN SUROESTE CON JABALÍ 2KG · 90013340000</t>
         </is>
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>90013320000</t>
+          <t>90013340000</t>
         </is>
       </c>
       <c r="C689" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -26947,16 +26942,16 @@
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>TOW CAÑÓN SUROESTE CON JABALÍ 2KG · 90013340000</t>
+          <t>TOW CAÑÓN SUROESTE CON JABALÍ 5.6KG · 90013260000</t>
         </is>
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>90013340000</t>
+          <t>90013260000</t>
         </is>
       </c>
       <c r="C690" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -26967,16 +26962,16 @@
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>TOW CAÑÓN SUROESTE CON JABALÍ 5.6KG · 90013260000</t>
+          <t>TOW FELINA DE LAS MONTANAS ROCOSAS 6.6KG · 90013210000</t>
         </is>
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>90013260000</t>
+          <t>90013210000</t>
         </is>
       </c>
       <c r="C691" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -26987,16 +26982,16 @@
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>TOW FELINA DE LAS MONTANAS ROCOSAS 6.6KG · 90013210000</t>
+          <t>TOW FÓRMULA FELINA TRUCHA Y SALMÓN AHUMA · 90013380000</t>
         </is>
       </c>
       <c r="B692" t="inlineStr">
         <is>
-          <t>90013210000</t>
+          <t>90013380000</t>
         </is>
       </c>
       <c r="C692" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -27007,16 +27002,16 @@
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>TOW FÓRMULA FELINA TRUCHA Y SALMÓN AHUMA · 90013380000</t>
+          <t>TOW HIGH  CACHORRO  BISONTE Y VENADO ASA · 90013280000</t>
         </is>
       </c>
       <c r="B693" t="inlineStr">
         <is>
-          <t>90013380000</t>
+          <t>90013280000</t>
         </is>
       </c>
       <c r="C693" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -27027,16 +27022,16 @@
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>TOW HIGH  CACHORRO  BISONTE Y VENADO ASA · 90013280000</t>
+          <t>TOW HIGH PRAIRIE BISONTE VENADO  12.2KG · 90013170000</t>
         </is>
       </c>
       <c r="B694" t="inlineStr">
         <is>
-          <t>90013280000</t>
+          <t>90013170000</t>
         </is>
       </c>
       <c r="C694" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -27047,16 +27042,16 @@
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t>TOW HIGH PRAIRIE BISONTE VENADO  12.2KG · 90013170000</t>
+          <t>TOW HIGH PRAIRIE CON BISONTE Y VENADO AS · 90013390000</t>
         </is>
       </c>
       <c r="B695" t="inlineStr">
         <is>
-          <t>90013170000</t>
+          <t>90013390000</t>
         </is>
       </c>
       <c r="C695" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -27067,16 +27062,16 @@
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>TOW HIGH PRAIRIE CON BISONTE Y VENADO AS · 90013390000</t>
+          <t>TOW HUMEDALES CANINOS CON AVES SILVESTRE · 90013270000</t>
         </is>
       </c>
       <c r="B696" t="inlineStr">
         <is>
-          <t>90013390000</t>
+          <t>90013270000</t>
         </is>
       </c>
       <c r="C696" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -27087,12 +27082,12 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>TOW HUMEDALES CANINOS CON AVES SILVESTRE · 90013270000</t>
+          <t>TOW HUMEDALES CANINOS CON AVES SILVESTRE · 90013330000</t>
         </is>
       </c>
       <c r="B697" t="inlineStr">
         <is>
-          <t>90013270000</t>
+          <t>90013330000</t>
         </is>
       </c>
       <c r="C697" t="n">
@@ -27107,16 +27102,16 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>TOW HUMEDALES CANINOS CON AVES SILVESTRE · 90013330000</t>
+          <t>TOW LOWLAND CREEK CON CODORNICES ASADAS · 90013410000</t>
         </is>
       </c>
       <c r="B698" t="inlineStr">
         <is>
-          <t>90013330000</t>
+          <t>90013410000</t>
         </is>
       </c>
       <c r="C698" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -27127,16 +27122,16 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>TOW LOWLAND CREEK CON CODORNICES ASADAS · 90013410000</t>
+          <t>TOW PACIFIC CACHORRO  SALMÓN AHUMADO 2KG · 90013370000</t>
         </is>
       </c>
       <c r="B699" t="inlineStr">
         <is>
-          <t>90013410000</t>
+          <t>90013370000</t>
         </is>
       </c>
       <c r="C699" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -27147,16 +27142,16 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>TOW PACIFIC CACHORRO  SALMÓN AHUMADO 2KG · 90013370000</t>
+          <t>TOW PACIFIC CACHORRO SALMÓN AHUMADO 5.6K · 90013300000</t>
         </is>
       </c>
       <c r="B700" t="inlineStr">
         <is>
-          <t>90013370000</t>
+          <t>90013300000</t>
         </is>
       </c>
       <c r="C700" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -27167,16 +27162,16 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t>TOW PACIFIC CACHORRO SALMÓN AHUMADO 5.6K · 90013300000</t>
+          <t>TOW PACIFIC S SALMON AHUMAD 12.2 KG · 90013230000</t>
         </is>
       </c>
       <c r="B701" t="inlineStr">
         <is>
-          <t>90013300000</t>
+          <t>90013230000</t>
         </is>
       </c>
       <c r="C701" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -27187,16 +27182,16 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>TOW PACIFIC S SALMON AHUMAD 12.2 KG · 90013230000</t>
+          <t>TOW PACIFIC ST CACHORRO SALMON 12.2 KG · 90013180000</t>
         </is>
       </c>
       <c r="B702" t="inlineStr">
         <is>
-          <t>90013230000</t>
+          <t>90013180000</t>
         </is>
       </c>
       <c r="C702" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -27207,16 +27202,16 @@
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>TOW PACIFIC ST CACHORRO SALMON 12.2 KG · 90013180000</t>
+          <t>TOW PACIFIC STREAM CON SALMÓN AHUMADO 5. · 90013250000</t>
         </is>
       </c>
       <c r="B703" t="inlineStr">
         <is>
-          <t>90013180000</t>
+          <t>90013250000</t>
         </is>
       </c>
       <c r="C703" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -27227,16 +27222,16 @@
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>TOW PACIFIC STREAM CON SALMÓN AHUMADO 5. · 90013250000</t>
+          <t>TOW PINAR CON CIERVO Y LEGUMBRES 2KG · 90013350000</t>
         </is>
       </c>
       <c r="B704" t="inlineStr">
         <is>
-          <t>90013250000</t>
+          <t>90013350000</t>
         </is>
       </c>
       <c r="C704" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -27247,12 +27242,12 @@
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>TOW PINAR CON CIERVO Y LEGUMBRES 2KG · 90013350000</t>
+          <t>TOW PINAR CON CIERVO Y LEGUMBRES 2KG · 90013360000</t>
         </is>
       </c>
       <c r="B705" t="inlineStr">
         <is>
-          <t>90013350000</t>
+          <t>90013360000</t>
         </is>
       </c>
       <c r="C705" t="n">
@@ -27267,12 +27262,12 @@
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>TOW PINAR CON CIERVO Y LEGUMBRES 2KG · 90013360000</t>
+          <t>TOW PINAR CON CIERVO Y LEGUMBRES 5.6KG · 90013240000</t>
         </is>
       </c>
       <c r="B706" t="inlineStr">
         <is>
-          <t>90013360000</t>
+          <t>90013240000</t>
         </is>
       </c>
       <c r="C706" t="n">
@@ -27287,16 +27282,16 @@
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>TOW PINAR CON CIERVO Y LEGUMBRES 5.6KG · 90013240000</t>
+          <t>TOW SIERRA MONTA CORDERO ASADO 12.2KG · 90013190000</t>
         </is>
       </c>
       <c r="B707" t="inlineStr">
         <is>
-          <t>90013240000</t>
+          <t>90013190000</t>
         </is>
       </c>
       <c r="C707" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -27307,16 +27302,16 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>TOW SIERRA MONTA CORDERO ASADO 12.2KG · 90013190000</t>
+          <t>TOW SIERRA MONTAÑA CON CORDERO ASADO 2KG · 90013400000</t>
         </is>
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>90013190000</t>
+          <t>90013400000</t>
         </is>
       </c>
       <c r="C708" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -27327,16 +27322,16 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>TOW SIERRA MONTAÑA CON CORDERO ASADO 2KG · 90013400000</t>
+          <t>TOW SIERRA MONTAÑA CON CORDERO ASADO 5.6 · 90013290000</t>
         </is>
       </c>
       <c r="B709" t="inlineStr">
         <is>
-          <t>90013400000</t>
+          <t>90013290000</t>
         </is>
       </c>
       <c r="C709" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -27347,36 +27342,36 @@
     <row r="710">
       <c r="A710" t="inlineStr">
         <is>
-          <t>TOW SIERRA MONTAÑA CON CORDERO ASADO 5.6 · 90013290000</t>
+          <t>D TETRA ALIMENTO COMUNITARIO 3.25OZ · 93518690000</t>
         </is>
       </c>
       <c r="B710" t="inlineStr">
         <is>
-          <t>90013290000</t>
+          <t>93518690000</t>
         </is>
       </c>
       <c r="C710" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>TASTE OF THE WILD</t>
+          <t>TETRA</t>
         </is>
       </c>
     </row>
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>D TETRA ALIMENTO COMUNITARIO 3.25OZ · 93518690000</t>
+          <t>D TETRA MINI PELLETS PARA BETTAS 0.15 · 93518660000</t>
         </is>
       </c>
       <c r="B711" t="inlineStr">
         <is>
-          <t>93518690000</t>
+          <t>93518660000</t>
         </is>
       </c>
       <c r="C711" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -27387,16 +27382,16 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>D TETRA MINI PELLETS PARA BETTAS 0.15 · 93518660000</t>
+          <t>D TETRA REPTOMIN 1.94 OZ · 90410040000</t>
         </is>
       </c>
       <c r="B712" t="inlineStr">
         <is>
-          <t>93518660000</t>
+          <t>90410040000</t>
         </is>
       </c>
       <c r="C712" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -27407,16 +27402,16 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>D TETRA REPTOMIN 1.94 OZ · 90410040000</t>
+          <t>D TETRA REPTOMIN 10.59OZ · 90409640000</t>
         </is>
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>90410040000</t>
+          <t>90409640000</t>
         </is>
       </c>
       <c r="C713" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -27427,16 +27422,16 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>D TETRA REPTOMIN 10.59OZ · 90409640000</t>
+          <t>TETRA ALGAE WAFER 2COLOR 12OZ · 90313380000</t>
         </is>
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>90409640000</t>
+          <t>90313380000</t>
         </is>
       </c>
       <c r="C714" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -27447,16 +27442,16 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>TETRA ALGAE WAFER 2COLOR 12OZ · 90313380000</t>
+          <t>TETRA ALIMENTO BETTA WORMS 0.98OZ · 93518650000</t>
         </is>
       </c>
       <c r="B715" t="inlineStr">
         <is>
-          <t>90313380000</t>
+          <t>93518650000</t>
         </is>
       </c>
       <c r="C715" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -27467,12 +27462,12 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>TETRA ALIMENTO BETTA WORMS 0.98OZ · 93518650000</t>
+          <t>TETRA BETTAMIN .81OZ  23GR · 90410310000</t>
         </is>
       </c>
       <c r="B716" t="inlineStr">
         <is>
-          <t>93518650000</t>
+          <t>90410310000</t>
         </is>
       </c>
       <c r="C716" t="n">
@@ -27487,16 +27482,16 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>TETRA BETTAMIN .81OZ  23GR · 90410310000</t>
+          <t>TETRA GEL FIN DE SEMANA 2 UD 24G · 90407210000</t>
         </is>
       </c>
       <c r="B717" t="inlineStr">
         <is>
-          <t>90410310000</t>
+          <t>90407210000</t>
         </is>
       </c>
       <c r="C717" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -27507,16 +27502,16 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>TETRA GEL FIN DE SEMANA 2 UD 24G · 90407210000</t>
+          <t>TETRA HOJUELA GOLDFISH 2.2OZ · 90409670000</t>
         </is>
       </c>
       <c r="B718" t="inlineStr">
         <is>
-          <t>90407210000</t>
+          <t>90409670000</t>
         </is>
       </c>
       <c r="C718" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -27527,16 +27522,16 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>TETRA HOJUELA GOLDFISH 2.2OZ · 90409670000</t>
+          <t>TETRA HOJUELAS GOLDFISH .42OZ · 90409900000</t>
         </is>
       </c>
       <c r="B719" t="inlineStr">
         <is>
-          <t>90409670000</t>
+          <t>90409900000</t>
         </is>
       </c>
       <c r="C719" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -27547,16 +27542,16 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>TETRA HOJUELAS GOLDFISH .42OZ · 90409900000</t>
+          <t>TETRA HOJUELAS GOLDFISH 3.53OZ · 90409910000</t>
         </is>
       </c>
       <c r="B720" t="inlineStr">
         <is>
-          <t>90409900000</t>
+          <t>90409910000</t>
         </is>
       </c>
       <c r="C720" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -27567,16 +27562,16 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>TETRA HOJUELAS GOLDFISH 3.53OZ · 90409910000</t>
+          <t>TETRA HOJUELAS TROPICAL 0.42OZ · 90409920000</t>
         </is>
       </c>
       <c r="B721" t="inlineStr">
         <is>
-          <t>90409910000</t>
+          <t>90409920000</t>
         </is>
       </c>
       <c r="C721" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -27587,16 +27582,16 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>TETRA HOJUELAS TROPICAL 0.42OZ · 90409920000</t>
+          <t>TETRA POND STICKS 2.53 LB · 90402260000</t>
         </is>
       </c>
       <c r="B722" t="inlineStr">
         <is>
-          <t>90409920000</t>
+          <t>90402260000</t>
         </is>
       </c>
       <c r="C722" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -27607,16 +27602,16 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>TETRA POND STICKS 2.53 LB · 90402260000</t>
+          <t>TETRA REPTOMINPRO TORTUGA JOVEN 12 · 93518680000</t>
         </is>
       </c>
       <c r="B723" t="inlineStr">
         <is>
-          <t>90402260000</t>
+          <t>93518680000</t>
         </is>
       </c>
       <c r="C723" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -27627,16 +27622,16 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>TETRA REPTOMINPRO TORTUGA JOVEN 12 · 93518680000</t>
+          <t>TETRAFIN HOJUELAS GOLDFISH 1 OZ · 90410990000</t>
         </is>
       </c>
       <c r="B724" t="inlineStr">
         <is>
-          <t>93518680000</t>
+          <t>90410990000</t>
         </is>
       </c>
       <c r="C724" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -27647,16 +27642,16 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>TETRAFIN HOJUELAS GOLDFISH 1 OZ · 90410990000</t>
+          <t>TETRAFIN HOJUELAS GOLDFISH 7.06 OZ · 90410490000</t>
         </is>
       </c>
       <c r="B725" t="inlineStr">
         <is>
-          <t>90410990000</t>
+          <t>90410490000</t>
         </is>
       </c>
       <c r="C725" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -27667,12 +27662,12 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>TETRAFIN HOJUELAS GOLDFISH 7.06 OZ · 90410490000</t>
+          <t>TETRAFIN PELLET FLOTANTE 1.87OZ · 90410020000</t>
         </is>
       </c>
       <c r="B726" t="inlineStr">
         <is>
-          <t>90410490000</t>
+          <t>90410020000</t>
         </is>
       </c>
       <c r="C726" t="n">
@@ -27687,16 +27682,16 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>TETRAFIN PELLET FLOTANTE 1.87OZ · 90410020000</t>
+          <t>TETRAMIN HOJUELAS 2.2OZ  62GR · 90410290000</t>
         </is>
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>90410020000</t>
+          <t>90410290000</t>
         </is>
       </c>
       <c r="C727" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -27707,36 +27702,36 @@
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>TETRAMIN HOJUELAS 2.2OZ  62GR · 90410290000</t>
+          <t>D TRIUMPH CAT CAFE SALMON Y TUNA 30LB · 935096300001</t>
         </is>
       </c>
       <c r="B728" t="inlineStr">
         <is>
-          <t>90410290000</t>
+          <t>935096300001</t>
         </is>
       </c>
       <c r="C728" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
-          <t>TETRA</t>
+          <t>TRIUMPH</t>
         </is>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>D TRIUMPH CAT CAFE SALMON Y TUNA 30LB · 935096300001</t>
+          <t>TRIUMPH FS GRAIN FREE SALMON 26L · 93501390000</t>
         </is>
       </c>
       <c r="B729" t="inlineStr">
         <is>
-          <t>935096300001</t>
+          <t>93501390000</t>
         </is>
       </c>
       <c r="C729" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -27747,36 +27742,36 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>TRIUMPH FS GRAIN FREE SALMON 26L · 93501390000</t>
+          <t>C VET LIFE NAT GASTROINTESTINAL 2 KG · 90010010000</t>
         </is>
       </c>
       <c r="B730" t="inlineStr">
         <is>
-          <t>93501390000</t>
+          <t>90010010000</t>
         </is>
       </c>
       <c r="C730" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
-          <t>TRIUMPH</t>
+          <t>VET LIFE</t>
         </is>
       </c>
     </row>
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>C VET LIFE NAT GASTROINTESTINAL 2 KG · 90010010000</t>
+          <t>C VET LIFE NAT OBED Y DIABETES 10 KG · 90010030000</t>
         </is>
       </c>
       <c r="B731" t="inlineStr">
         <is>
-          <t>90010010000</t>
+          <t>90010030000</t>
         </is>
       </c>
       <c r="C731" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -27787,16 +27782,16 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>C VET LIFE NAT OBED Y DIABETES 10 KG · 90010030000</t>
+          <t>C VET LIFE NAT OBEI Y DIABETES 2 KG · 90010040000</t>
         </is>
       </c>
       <c r="B732" t="inlineStr">
         <is>
-          <t>90010030000</t>
+          <t>90010040000</t>
         </is>
       </c>
       <c r="C732" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -27807,16 +27802,16 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>C VET LIFE NAT OBEI Y DIABETES 2 KG · 90010040000</t>
+          <t>C VET LIFE NAT RENAL 2 KG · 90010050000</t>
         </is>
       </c>
       <c r="B733" t="inlineStr">
         <is>
-          <t>90010040000</t>
+          <t>90010050000</t>
         </is>
       </c>
       <c r="C733" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -27827,16 +27822,16 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>C VET LIFE NAT RENAL 2 KG · 90010050000</t>
+          <t>C VET LIFE NAT URI OSSA 2 KG · 90010060000</t>
         </is>
       </c>
       <c r="B734" t="inlineStr">
         <is>
-          <t>90010050000</t>
+          <t>90010060000</t>
         </is>
       </c>
       <c r="C734" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -27847,16 +27842,16 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>C VET LIFE NAT URI OSSA 2 KG · 90010060000</t>
+          <t>C VET LIFE URI STRUVITE 2 KG · 90010070000</t>
         </is>
       </c>
       <c r="B735" t="inlineStr">
         <is>
-          <t>90010060000</t>
+          <t>90010070000</t>
         </is>
       </c>
       <c r="C735" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -27867,36 +27862,36 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>C VET LIFE URI STRUVITE 2 KG · 90010070000</t>
+          <t>WHISKAS  POUCH ATUN SARDINA 85GR. · 90028540000</t>
         </is>
       </c>
       <c r="B736" t="inlineStr">
         <is>
-          <t>90010070000</t>
+          <t>90028540000</t>
         </is>
       </c>
       <c r="C736" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
-          <t>VET LIFE</t>
+          <t>WHISKAS</t>
         </is>
       </c>
     </row>
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>WHISKAS  POUCH ATUN SARDINA 85GR. · 90028540000</t>
+          <t>WHISKAS CARNE ORIGINAL 1.5KG · 90408360000</t>
         </is>
       </c>
       <c r="B737" t="inlineStr">
         <is>
-          <t>90028540000</t>
+          <t>90408360000</t>
         </is>
       </c>
       <c r="C737" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -27907,16 +27902,16 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>WHISKAS CARNE ORIGINAL 1.5KG · 90408360000</t>
+          <t>WHISKAS GATITOS 1.4KG · 93515190000</t>
         </is>
       </c>
       <c r="B738" t="inlineStr">
         <is>
-          <t>90408360000</t>
+          <t>93515190000</t>
         </is>
       </c>
       <c r="C738" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -27927,16 +27922,16 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>WHISKAS GATITOS 1.4KG · 93515190000</t>
+          <t>WHISKAS MIX PROTE SECO 1.5KG · 90028510000</t>
         </is>
       </c>
       <c r="B739" t="inlineStr">
         <is>
-          <t>93515190000</t>
+          <t>90028510000</t>
         </is>
       </c>
       <c r="C739" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -27947,16 +27942,16 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>WHISKAS MIX PROTE SECO 1.5KG · 90028510000</t>
+          <t>WHISKAS ORIGINAL SABOR CARNE 500G · 93518270000</t>
         </is>
       </c>
       <c r="B740" t="inlineStr">
         <is>
-          <t>90028510000</t>
+          <t>93518270000</t>
         </is>
       </c>
       <c r="C740" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -27967,16 +27962,16 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>WHISKAS ORIGINAL SABOR CARNE 500G · 93518270000</t>
+          <t>WHISKAS PESCADO 1.5KG · 90301130000</t>
         </is>
       </c>
       <c r="B741" t="inlineStr">
         <is>
-          <t>93518270000</t>
+          <t>90301130000</t>
         </is>
       </c>
       <c r="C741" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -27987,16 +27982,16 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>WHISKAS PESCADO 1.5KG · 90301130000</t>
+          <t>WHISKAS POUCH ATÚN 85GR. · 90028530000</t>
         </is>
       </c>
       <c r="B742" t="inlineStr">
         <is>
-          <t>90301130000</t>
+          <t>90028530000</t>
         </is>
       </c>
       <c r="C742" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -28007,16 +28002,16 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>WHISKAS POUCH ATÚN 85GR. · 90028530000</t>
+          <t>WHISKAS POUCH POLLO 85GR · 90409050000</t>
         </is>
       </c>
       <c r="B743" t="inlineStr">
         <is>
-          <t>90028530000</t>
+          <t>90409050000</t>
         </is>
       </c>
       <c r="C743" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -28027,16 +28022,16 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>WHISKAS POUCH POLLO 85GR · 90409050000</t>
+          <t>WHISKAS POUCH POLLO Y PAVO 85GR. · 90028550000</t>
         </is>
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>90409050000</t>
+          <t>90028550000</t>
         </is>
       </c>
       <c r="C744" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -28047,16 +28042,16 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>WHISKAS POUCH POLLO Y PAVO 85GR. · 90028550000</t>
+          <t>WHISKAS POUCH RES  85GR · 90409070000</t>
         </is>
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>90028550000</t>
+          <t>90409070000</t>
         </is>
       </c>
       <c r="C745" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -28067,36 +28062,36 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>WHISKAS POUCH RES  85GR · 90409070000</t>
+          <t>D ZM ALIM GOURMET TORTUGA TERRESTR 12 · 93517610000</t>
         </is>
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>90409070000</t>
+          <t>93517610000</t>
         </is>
       </c>
       <c r="C746" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
-          <t>WHISKAS</t>
+          <t>ZOO MED</t>
         </is>
       </c>
     </row>
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>D ZM ALIM GOURMET TORTUGA TERRESTR 12 · 93517610000</t>
+          <t>D ZM ALIM GOURMET/ TORTUGA TERRESTRE · 93517600000</t>
         </is>
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>93517610000</t>
+          <t>93517600000</t>
         </is>
       </c>
       <c r="C747" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -28107,16 +28102,16 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>D ZM ALIM GOURMET/ TORTUGA TERRESTRE · 93517600000</t>
+          <t>D ZM ALIMENTO EN BLOQUE P TORTUGAS 1 · 93517500000</t>
         </is>
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>93517600000</t>
+          <t>93517500000</t>
         </is>
       </c>
       <c r="C748" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -28127,16 +28122,16 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>D ZM ALIMENTO EN BLOQUE P TORTUGAS 1 · 93517500000</t>
+          <t>D ZM ALIMENTO EN BLOQUE P TORTUGAS 5 · 93517490000</t>
         </is>
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>93517500000</t>
+          <t>93517490000</t>
         </is>
       </c>
       <c r="C749" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -28147,16 +28142,16 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>D ZM ALIMENTO EN BLOQUE P TORTUGAS 5 · 93517490000</t>
+          <t>D ZM ALIMENTO EN BLOQUES P/BETTAS · 93514820000</t>
         </is>
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>93517490000</t>
+          <t>93514820000</t>
         </is>
       </c>
       <c r="C750" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -28167,16 +28162,16 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>D ZM ALIMENTO EN BLOQUES P/BETTAS · 93514820000</t>
+          <t>D ZM ALIMENTO VARIADO P BETTA 0.12OZ · 93504390000</t>
         </is>
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>93514820000</t>
+          <t>93504390000</t>
         </is>
       </c>
       <c r="C751" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -28187,16 +28182,16 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>D ZM ALIMENTO VARIADO P BETTA 0.12OZ · 93504390000</t>
+          <t>D ZM CALCIO PARA AVES 3OZ · 93514810000</t>
         </is>
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>93504390000</t>
+          <t>93514810000</t>
         </is>
       </c>
       <c r="C752" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -28207,16 +28202,16 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>D ZM CALCIO PARA AVES 3OZ · 93514810000</t>
+          <t>D ZM DRAGON BARBUDO ADULTO 10OZ. · 90415500000</t>
         </is>
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>93514810000</t>
+          <t>90415500000</t>
         </is>
       </c>
       <c r="C753" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -28227,12 +28222,12 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>D ZM DRAGON BARBUDO ADULTO 10OZ. · 90415500000</t>
+          <t>D ZM DRAGON BARBUDO JOVEN 2OZ. · 90415480000</t>
         </is>
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>90415500000</t>
+          <t>90415480000</t>
         </is>
       </c>
       <c r="C754" t="n">
@@ -28247,16 +28242,16 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t>D ZM DRAGON BARBUDO JOVEN 2OZ. · 90415480000</t>
+          <t>D ZM LATA REPTILES PAPAYA 113GR · 90416010000</t>
         </is>
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>90415480000</t>
+          <t>90416010000</t>
         </is>
       </c>
       <c r="C755" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -28267,16 +28262,16 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>D ZM LATA REPTILES PAPAYA 113GR · 90416010000</t>
+          <t>D ZM SNACK DE FLORES P/LAGARTIJAS 6G · 93517660000</t>
         </is>
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>90416010000</t>
+          <t>93517660000</t>
         </is>
       </c>
       <c r="C756" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -28287,16 +28282,16 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>D ZM SNACK DE FLORES P/LAGARTIJAS 6G · 93517660000</t>
+          <t>D ZM SNACK DE FLORES P/TORTUGAS 6G · 93517650000</t>
         </is>
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>93517660000</t>
+          <t>93517650000</t>
         </is>
       </c>
       <c r="C757" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -28307,16 +28302,16 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>D ZM SNACK DE FLORES P/TORTUGAS 6G · 93517650000</t>
+          <t>D ZM SUPLEMENTO VITAMINICO P/AVES · 93514800000</t>
         </is>
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>93517650000</t>
+          <t>93514800000</t>
         </is>
       </c>
       <c r="C758" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -28327,16 +28322,16 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>D ZM SUPLEMENTO VITAMINICO P/AVES · 93514800000</t>
+          <t>ZM ALIM NATURAL TORTUGA ACUATICA 7 · 93517560000</t>
         </is>
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>93514800000</t>
+          <t>93517560000</t>
         </is>
       </c>
       <c r="C759" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -28347,12 +28342,12 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>ZM ALIM NATURAL TORTUGA ACUATICA 7 · 93517560000</t>
+          <t>ZM ALIM TORTUGAS REPTISTICKS 141GR · 90415930000</t>
         </is>
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>93517560000</t>
+          <t>90415930000</t>
         </is>
       </c>
       <c r="C760" t="n">
@@ -28367,16 +28362,16 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>ZM ALIM TORTUGAS REPTISTICKS 141GR · 90415930000</t>
+          <t>ZM ALIM TORTUGAS REPTISTICKS 28GR · 90415880000</t>
         </is>
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>90415930000</t>
+          <t>90415880000</t>
         </is>
       </c>
       <c r="C761" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -28387,16 +28382,16 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>ZM ALIM TORTUGAS REPTISTICKS 28GR · 90415880000</t>
+          <t>ZM ALIMENTO EN BLOQUE PARA PECES 1 · 93517470000</t>
         </is>
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>90415880000</t>
+          <t>93517470000</t>
         </is>
       </c>
       <c r="C762" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -28407,16 +28402,16 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>ZM ALIMENTO EN BLOQUE PARA PECES 1 · 93517470000</t>
+          <t>ZM ALIMENTO EN BLOQUE PARA PECES 6 · 93517480000</t>
         </is>
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>93517470000</t>
+          <t>93517480000</t>
         </is>
       </c>
       <c r="C763" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -28427,16 +28422,16 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>ZM ALIMENTO EN BLOQUE PARA PECES 6 · 93517480000</t>
+          <t>ZM ALIMENTO P/TORTUGA ACUAT 425G · 90410650000</t>
         </is>
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>93517480000</t>
+          <t>90410650000</t>
         </is>
       </c>
       <c r="C764" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -28447,12 +28442,12 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>ZM ALIMENTO P/TORTUGA ACUAT 425G · 90410650000</t>
+          <t>ZM ALIMENTO TORTUGA ACUATICA  52G · 90410660000</t>
         </is>
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>90410650000</t>
+          <t>90410660000</t>
         </is>
       </c>
       <c r="C765" t="n">
@@ -28467,12 +28462,12 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>ZM ALIMENTO TORTUGA ACUATICA  52G · 90410660000</t>
+          <t>ZM CALCIO PQNO CON VEGETALES P/AVES · 93503060000</t>
         </is>
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>90410660000</t>
+          <t>93503060000</t>
         </is>
       </c>
       <c r="C766" t="n">
@@ -28487,16 +28482,16 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>ZM CALCIO PQNO CON VEGETALES P/AVES · 93503060000</t>
+          <t>ZM ELECTROLITOS PARA REPTILES 8OZ · 93519210000</t>
         </is>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>93503060000</t>
+          <t>93519210000</t>
         </is>
       </c>
       <c r="C767" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -28507,16 +28502,16 @@
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>ZM ELECTROLITOS PARA REPTILES 8OZ · 93519210000</t>
+          <t>ZM MICRO PELLET P/BETTA 0.12OZ · 93514830000</t>
         </is>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>93519210000</t>
+          <t>93514830000</t>
         </is>
       </c>
       <c r="C768" t="n">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -28527,16 +28522,16 @@
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>ZM MICRO PELLET P/BETTA 0.12OZ · 93514830000</t>
+          <t>ZM MICRO PELLETS P/BETTAS 0.65OZ · 93514840000</t>
         </is>
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>93514830000</t>
+          <t>93514840000</t>
         </is>
       </c>
       <c r="C769" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -28544,57 +28539,37 @@
         </is>
       </c>
     </row>
-    <row r="770">
-      <c r="A770" t="inlineStr">
-        <is>
-          <t>ZM MICRO PELLETS P/BETTAS 0.65OZ · 93514840000</t>
-        </is>
-      </c>
-      <c r="B770" t="inlineStr">
-        <is>
-          <t>93514840000</t>
-        </is>
-      </c>
-      <c r="C770" t="n">
-        <v>43</v>
-      </c>
-      <c r="D770" t="inlineStr">
-        <is>
-          <t>ZOO MED</t>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>P&amp;G | ALBROOK MALL</t>
         </is>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>Sucursal</t>
-        </is>
-      </c>
-      <c r="B772" t="inlineStr">
-        <is>
-          <t>P&amp;G | ALBROOK MALL</t>
-        </is>
+          <t>Índice</t>
+        </is>
+      </c>
+      <c r="B772" t="n">
+        <v>82</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>Índice</t>
-        </is>
-      </c>
-      <c r="B773" t="n">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="774">
-      <c r="A774" t="inlineStr">
-        <is>
           <t>Inventario al</t>
         </is>
       </c>
-      <c r="B774" t="inlineStr">
-        <is>
-          <t>28.10.2026</t>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>29.10.2026</t>
         </is>
       </c>
     </row>
